--- a/src/attributions/attributions_saliency_traj_102.xlsx
+++ b/src/attributions/attributions_saliency_traj_102.xlsx
@@ -1568,571 +1568,571 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5.189993316889741e-05</v>
+        <v>0.2381978631019592</v>
       </c>
       <c r="B3" t="n">
-        <v>1.563051409902982e-05</v>
+        <v>0.08182843029499054</v>
       </c>
       <c r="C3" t="n">
-        <v>6.485354970209301e-05</v>
+        <v>0.1508575677871704</v>
       </c>
       <c r="D3" t="n">
-        <v>5.316050373949111e-05</v>
+        <v>0.08492419123649597</v>
       </c>
       <c r="E3" t="n">
-        <v>7.15068745194003e-05</v>
+        <v>0.2748512029647827</v>
       </c>
       <c r="F3" t="n">
-        <v>2.616070742078591e-05</v>
+        <v>0.1280561536550522</v>
       </c>
       <c r="G3" t="n">
-        <v>3.079898306168616e-06</v>
+        <v>0.04899961873888969</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0001156671060016379</v>
+        <v>0.01732317917048931</v>
       </c>
       <c r="I3" t="n">
-        <v>8.289180550491437e-05</v>
+        <v>0.05923226475715637</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000136096597998403</v>
+        <v>0.2202188819646835</v>
       </c>
       <c r="K3" t="n">
-        <v>5.125364987179637e-05</v>
+        <v>0.01332912780344486</v>
       </c>
       <c r="L3" t="n">
-        <v>8.301420893985778e-05</v>
+        <v>0.1135454922914505</v>
       </c>
       <c r="M3" t="n">
-        <v>8.604843606008217e-05</v>
+        <v>0.08879624307155609</v>
       </c>
       <c r="N3" t="n">
-        <v>0.000101040983281564</v>
+        <v>0.187133714556694</v>
       </c>
       <c r="O3" t="n">
-        <v>5.870152563147712e-06</v>
+        <v>0.16340371966362</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0001634650107007474</v>
+        <v>0.09209554642438889</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.563018668093719e-05</v>
+        <v>0.1182769611477852</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002018415107158944</v>
+        <v>0.06198094412684441</v>
       </c>
       <c r="S3" t="n">
-        <v>1.21854664030252e-05</v>
+        <v>0.0001260023564100266</v>
       </c>
       <c r="T3" t="n">
-        <v>5.619269359158352e-06</v>
+        <v>0.1319640278816223</v>
       </c>
       <c r="U3" t="n">
-        <v>5.03015544381924e-05</v>
+        <v>0.06016401946544647</v>
       </c>
       <c r="V3" t="n">
-        <v>8.988036279333755e-05</v>
+        <v>0.02372349053621292</v>
       </c>
       <c r="W3" t="n">
-        <v>5.39300890523009e-05</v>
+        <v>0.1077662482857704</v>
       </c>
       <c r="X3" t="n">
-        <v>9.165373194264248e-05</v>
+        <v>0.09345885366201401</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.516084249597043e-05</v>
+        <v>0.01854829862713814</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0001773256226442754</v>
+        <v>0.0671234205365181</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.327754934114637e-06</v>
+        <v>0.004720168188214302</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0001699756539892405</v>
+        <v>0.07406289875507355</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.74890073039569e-05</v>
+        <v>0.06373174488544464</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.214351403992623e-05</v>
+        <v>0.00840351078659296</v>
       </c>
       <c r="AE3" t="n">
-        <v>4.70542763650883e-05</v>
+        <v>0.06920542567968369</v>
       </c>
       <c r="AF3" t="n">
-        <v>7.700365677010268e-05</v>
+        <v>0.06366416066884995</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.27260994608514e-05</v>
+        <v>0.03183694928884506</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.307513932464644e-05</v>
+        <v>0.03835412114858627</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.091028313268907e-05</v>
+        <v>0.06604128330945969</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.824596569756977e-05</v>
+        <v>0.05684575811028481</v>
       </c>
       <c r="AK3" t="n">
-        <v>6.836672582721803e-06</v>
+        <v>0.06894432753324509</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.450850585475564e-05</v>
+        <v>0.1629557758569717</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0001219544792547822</v>
+        <v>0.01905153505504131</v>
       </c>
       <c r="AN3" t="n">
-        <v>5.879523087060079e-05</v>
+        <v>0.02787614986300468</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0001231364294653758</v>
+        <v>0.1186126172542572</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.150125874322839e-05</v>
+        <v>0.04586409777402878</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.923467248678207e-06</v>
+        <v>0.02166150137782097</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.897109152399935e-05</v>
+        <v>0.04461966827511787</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.825220533646643e-05</v>
+        <v>0.002478456124663353</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.214980850112624e-05</v>
+        <v>0.1175573766231537</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.668592449277639e-05</v>
+        <v>0.1082406491041183</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0002111235517077148</v>
+        <v>0.01082473900169134</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.004888175288215e-06</v>
+        <v>0.05103724077343941</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0003525904903654009</v>
+        <v>0.1693534106016159</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0002091872593155131</v>
+        <v>0.1230788230895996</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.904604404349811e-05</v>
+        <v>0.05545642971992493</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0001680782588664442</v>
+        <v>0.04055879265069962</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0002429686428513378</v>
+        <v>0.09525139629840851</v>
       </c>
       <c r="BC3" t="n">
-        <v>9.320883691543713e-06</v>
+        <v>0.005432024598121643</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.017953763948753e-06</v>
+        <v>0.03470730781555176</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0001239915727637708</v>
+        <v>0.04346705228090286</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.980014298576862e-05</v>
+        <v>0.0112580880522728</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.0002345909742871299</v>
+        <v>0.02509541064500809</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.515897671808489e-06</v>
+        <v>0.03343319147825241</v>
       </c>
       <c r="BI3" t="n">
-        <v>5.826971028000116e-05</v>
+        <v>0.002648855093866587</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.000174927365151234</v>
+        <v>0.09576098620891571</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.0001859124022303149</v>
+        <v>0.0626300722360611</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.471200812375173e-05</v>
+        <v>0.003465456888079643</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.0001396057778038085</v>
+        <v>0.07428616285324097</v>
       </c>
       <c r="BN3" t="n">
-        <v>2.36415071412921e-05</v>
+        <v>0.01007295772433281</v>
       </c>
       <c r="BO3" t="n">
-        <v>5.905552097829059e-05</v>
+        <v>0.06578835844993591</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0001510149595560506</v>
+        <v>0.100808247923851</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0001503576786490157</v>
+        <v>0.001110587734729052</v>
       </c>
       <c r="BR3" t="n">
-        <v>1.096082451113034e-05</v>
+        <v>0.03068319708108902</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0001229594927281141</v>
+        <v>0.01900564134120941</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0001268389605684206</v>
+        <v>0.02901245281100273</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.286022052227054e-05</v>
+        <v>0.1077269315719604</v>
       </c>
       <c r="BV3" t="n">
-        <v>8.663395419716835e-05</v>
+        <v>0.1688940078020096</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.987166463863105e-05</v>
+        <v>0.03887319564819336</v>
       </c>
       <c r="BX3" t="n">
-        <v>4.026326496386901e-05</v>
+        <v>0.01004507299512625</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.000178313217475079</v>
+        <v>0.1598004400730133</v>
       </c>
       <c r="BZ3" t="n">
-        <v>6.908326031407341e-05</v>
+        <v>0.01195063255727291</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.844347389123868e-05</v>
+        <v>0.02716728299856186</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.143979847664014e-05</v>
+        <v>0.1066237166523933</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0001497748162364587</v>
+        <v>0.00432099774479866</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.769057002500631e-05</v>
+        <v>0.09060269594192505</v>
       </c>
       <c r="CE3" t="n">
-        <v>7.542385719716549e-05</v>
+        <v>0.02689776569604874</v>
       </c>
       <c r="CF3" t="n">
-        <v>9.994570064009167e-06</v>
+        <v>0.01016292441636324</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.079143450828269e-05</v>
+        <v>0.01652563735842705</v>
       </c>
       <c r="CH3" t="n">
-        <v>3.264618499088101e-05</v>
+        <v>0.06467656046152115</v>
       </c>
       <c r="CI3" t="n">
-        <v>4.861372872255743e-05</v>
+        <v>0.004365975968539715</v>
       </c>
       <c r="CJ3" t="n">
-        <v>8.169750799424946e-06</v>
+        <v>0.01214772090315819</v>
       </c>
       <c r="CK3" t="n">
-        <v>5.703309579985216e-05</v>
+        <v>0.01539758965373039</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.105376734107267e-05</v>
+        <v>0.02134132757782936</v>
       </c>
       <c r="CM3" t="n">
-        <v>9.859979763859883e-05</v>
+        <v>0.08717760443687439</v>
       </c>
       <c r="CN3" t="n">
-        <v>9.578649041941389e-05</v>
+        <v>0.1206285655498505</v>
       </c>
       <c r="CO3" t="n">
-        <v>6.591290002688766e-06</v>
+        <v>0.1273938864469528</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.0001279312709812075</v>
+        <v>0.1053009405732155</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0001403732458129525</v>
+        <v>0.01940402388572693</v>
       </c>
       <c r="CR3" t="n">
-        <v>7.088310667313635e-05</v>
+        <v>0.02040832862257957</v>
       </c>
       <c r="CS3" t="n">
-        <v>5.606441118288785e-05</v>
+        <v>0.03600973263382912</v>
       </c>
       <c r="CT3" t="n">
-        <v>5.642769974656403e-05</v>
+        <v>0.04477687925100327</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.0002011577307712287</v>
+        <v>0.07003658264875412</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.612038249731995e-05</v>
+        <v>0.07976187765598297</v>
       </c>
       <c r="CW3" t="n">
-        <v>6.37440534774214e-05</v>
+        <v>0.03713452443480492</v>
       </c>
       <c r="CX3" t="n">
-        <v>2.950649650301784e-05</v>
+        <v>0.01102183014154434</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.899617018352728e-05</v>
+        <v>0.002039692830294371</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.674861389095895e-05</v>
+        <v>0.05354675650596619</v>
       </c>
       <c r="DA3" t="n">
-        <v>6.357936945278198e-05</v>
+        <v>0.001078019384294748</v>
       </c>
       <c r="DB3" t="n">
-        <v>6.575788574991748e-06</v>
+        <v>0.0147566944360733</v>
       </c>
       <c r="DC3" t="n">
-        <v>3.89764754800126e-05</v>
+        <v>0.004031900316476822</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.318040242244024e-05</v>
+        <v>0.01760426536202431</v>
       </c>
       <c r="DE3" t="n">
-        <v>3.460938023636118e-05</v>
+        <v>0.1311893910169601</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.0001038362679537386</v>
+        <v>0.01009168289601803</v>
       </c>
       <c r="DG3" t="n">
-        <v>8.0887257354334e-05</v>
+        <v>0.0953301340341568</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.000163742748554796</v>
+        <v>0.01736996322870255</v>
       </c>
       <c r="DI3" t="n">
-        <v>2.344863969483413e-05</v>
+        <v>0.1396190971136093</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.000146168764331378</v>
+        <v>0.1611411720514297</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.0001394386636093259</v>
+        <v>0.03554839640855789</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.0003018618444912136</v>
+        <v>0.04217721521854401</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.0001936137850861996</v>
+        <v>0.1010186970233917</v>
       </c>
       <c r="DN3" t="n">
-        <v>3.498039586702362e-05</v>
+        <v>0.09091570973396301</v>
       </c>
       <c r="DO3" t="n">
-        <v>8.565964526496828e-05</v>
+        <v>0.0575798787176609</v>
       </c>
       <c r="DP3" t="n">
-        <v>6.091843897593208e-05</v>
+        <v>0.03426843509078026</v>
       </c>
       <c r="DQ3" t="n">
-        <v>1.800651079975069e-05</v>
+        <v>0.002697245450690389</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.0001881516363937408</v>
+        <v>0.06755957007408142</v>
       </c>
       <c r="DS3" t="n">
-        <v>5.473965211422183e-05</v>
+        <v>0.03552260249853134</v>
       </c>
       <c r="DT3" t="n">
-        <v>3.606268001021817e-05</v>
+        <v>0.06394031643867493</v>
       </c>
       <c r="DU3" t="n">
-        <v>6.796697107347427e-06</v>
+        <v>0.03267247229814529</v>
       </c>
       <c r="DV3" t="n">
-        <v>2.115360075549688e-05</v>
+        <v>0.01517143473029137</v>
       </c>
       <c r="DW3" t="n">
-        <v>2.564661144788261e-06</v>
+        <v>0.004464756231755018</v>
       </c>
       <c r="DX3" t="n">
-        <v>2.431214670650661e-05</v>
+        <v>0.001798417884856462</v>
       </c>
       <c r="DY3" t="n">
-        <v>3.74576666217763e-05</v>
+        <v>0.03239233046770096</v>
       </c>
       <c r="DZ3" t="n">
-        <v>7.083251693984494e-05</v>
+        <v>0.1694376766681671</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.0001067464909283444</v>
+        <v>0.1383458822965622</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.0001308614882873371</v>
+        <v>0.01173963211476803</v>
       </c>
       <c r="EC3" t="n">
-        <v>3.980076871812344e-05</v>
+        <v>0.08502539992332458</v>
       </c>
       <c r="ED3" t="n">
-        <v>6.620925705647096e-05</v>
+        <v>0.1199975088238716</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.0001343356125289574</v>
+        <v>0.01583044417202473</v>
       </c>
       <c r="EF3" t="n">
-        <v>1.413720201526303e-05</v>
+        <v>0.02864369377493858</v>
       </c>
       <c r="EG3" t="n">
-        <v>8.679378515807912e-05</v>
+        <v>0.02938888780772686</v>
       </c>
       <c r="EH3" t="n">
-        <v>5.168798816157505e-05</v>
+        <v>0.05013615265488625</v>
       </c>
       <c r="EI3" t="n">
-        <v>4.321233427617699e-05</v>
+        <v>0.01546619087457657</v>
       </c>
       <c r="EJ3" t="n">
-        <v>8.328801413881592e-06</v>
+        <v>0.02542009949684143</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.0001813132112147287</v>
+        <v>0.05128049477934837</v>
       </c>
       <c r="EL3" t="n">
-        <v>5.317381692293566e-06</v>
+        <v>0.005871851928532124</v>
       </c>
       <c r="EM3" t="n">
-        <v>3.738927625818178e-05</v>
+        <v>0.02923602238297462</v>
       </c>
       <c r="EN3" t="n">
-        <v>2.380416481173597e-05</v>
+        <v>0.04783526808023453</v>
       </c>
       <c r="EO3" t="n">
-        <v>7.98989822214935e-06</v>
+        <v>0.05657374858856201</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.0001686536124907434</v>
+        <v>0.03458455950021744</v>
       </c>
       <c r="EQ3" t="n">
-        <v>4.207118763588369e-06</v>
+        <v>0.1297986209392548</v>
       </c>
       <c r="ER3" t="n">
-        <v>1.376607269776287e-05</v>
+        <v>0.02057560533285141</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.0001236945536220446</v>
+        <v>0.07541841268539429</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.0001133769765147008</v>
+        <v>0.06707701086997986</v>
       </c>
       <c r="EU3" t="n">
-        <v>3.299373929621652e-05</v>
+        <v>0.01852316781878471</v>
       </c>
       <c r="EV3" t="n">
-        <v>8.046828588703647e-05</v>
+        <v>0.08787992596626282</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.0001128859148593619</v>
+        <v>0.05466137826442719</v>
       </c>
       <c r="EX3" t="n">
-        <v>2.247414158773609e-05</v>
+        <v>0.08014100790023804</v>
       </c>
       <c r="EY3" t="n">
-        <v>6.366193701978773e-05</v>
+        <v>0.04731689393520355</v>
       </c>
       <c r="EZ3" t="n">
-        <v>5.890065949643031e-06</v>
+        <v>0.0155551340430975</v>
       </c>
       <c r="FA3" t="n">
-        <v>2.516405584174208e-05</v>
+        <v>0.03340385854244232</v>
       </c>
       <c r="FB3" t="n">
-        <v>1.602333213668317e-05</v>
+        <v>0.05833379924297333</v>
       </c>
       <c r="FC3" t="n">
-        <v>4.518025525612757e-05</v>
+        <v>0.003583180718123913</v>
       </c>
       <c r="FD3" t="n">
-        <v>1.20100230560638e-06</v>
+        <v>0.02578197419643402</v>
       </c>
       <c r="FE3" t="n">
-        <v>7.270224887179211e-05</v>
+        <v>0.01721997559070587</v>
       </c>
       <c r="FF3" t="n">
-        <v>2.041307561739814e-05</v>
+        <v>0.01888875290751457</v>
       </c>
       <c r="FG3" t="n">
-        <v>3.789177571889013e-05</v>
+        <v>0.04679408296942711</v>
       </c>
       <c r="FH3" t="n">
-        <v>6.06854009674862e-05</v>
+        <v>0.010718809440732</v>
       </c>
       <c r="FI3" t="n">
-        <v>3.723229019669816e-05</v>
+        <v>0.07560848444700241</v>
       </c>
       <c r="FJ3" t="n">
-        <v>1.983710535569116e-05</v>
+        <v>0.1211565285921097</v>
       </c>
       <c r="FK3" t="n">
-        <v>3.647523772087879e-05</v>
+        <v>0.04303396865725517</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.0001842674537329003</v>
+        <v>0.06959201395511627</v>
       </c>
       <c r="FM3" t="n">
-        <v>2.984878665301949e-05</v>
+        <v>0.07032860815525055</v>
       </c>
       <c r="FN3" t="n">
-        <v>9.510523341305088e-06</v>
+        <v>0.02131664007902145</v>
       </c>
       <c r="FO3" t="n">
-        <v>1.054986842063954e-05</v>
+        <v>0.005577478557825089</v>
       </c>
       <c r="FP3" t="n">
-        <v>7.958376954775304e-05</v>
+        <v>0.04940889403223991</v>
       </c>
       <c r="FQ3" t="n">
-        <v>3.23620843118988e-05</v>
+        <v>0.03844630345702171</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.0001560463133500889</v>
+        <v>0.1181179285049438</v>
       </c>
       <c r="FS3" t="n">
-        <v>3.365222437423654e-05</v>
+        <v>0.04244712367653847</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.0001373730337945744</v>
+        <v>0.05225635319948196</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.0002723618526943028</v>
+        <v>0.1079695373773575</v>
       </c>
       <c r="FV3" t="n">
-        <v>5.998561391606927e-05</v>
+        <v>0.05667632818222046</v>
       </c>
       <c r="FW3" t="n">
-        <v>9.468844655202702e-05</v>
+        <v>0.04210625216364861</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.0001498115598224103</v>
+        <v>0.1108833700418472</v>
       </c>
       <c r="FY3" t="n">
-        <v>7.151073077693582e-05</v>
+        <v>0.0463731437921524</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.0001135041457018815</v>
+        <v>0.08620394021272659</v>
       </c>
       <c r="GA3" t="n">
-        <v>5.150712604518048e-05</v>
+        <v>0.0216287337243557</v>
       </c>
       <c r="GB3" t="n">
-        <v>2.080818558169995e-05</v>
+        <v>0.07377826422452927</v>
       </c>
       <c r="GC3" t="n">
-        <v>1.425862592441263e-07</v>
+        <v>0.1084318310022354</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.0002294718287885189</v>
+        <v>0.08188501745462418</v>
       </c>
       <c r="GE3" t="n">
-        <v>5.115530075272545e-05</v>
+        <v>0.01747760735452175</v>
       </c>
       <c r="GF3" t="n">
-        <v>6.685686093987897e-05</v>
+        <v>0.0322839766740799</v>
       </c>
       <c r="GG3" t="n">
-        <v>2.122647310898174e-05</v>
+        <v>0.04446448013186455</v>
       </c>
     </row>
     <row r="4">
@@ -2706,2847 +2706,2847 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0006491406820714474</v>
+        <v>0.002182845026254654</v>
       </c>
       <c r="B5" t="n">
-        <v>0.06526359170675278</v>
+        <v>0.6721799373626709</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001221016980707645</v>
+        <v>0.07672334462404251</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03319618850946426</v>
+        <v>0.3586183190345764</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01653467491269112</v>
+        <v>0.1588535755872726</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001234570285305381</v>
+        <v>0.1763486117124557</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003028228413313627</v>
+        <v>0.09098762273788452</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003531643887981772</v>
+        <v>0.04943311959505081</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006854863837361336</v>
+        <v>0.04006259143352509</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006695999763906002</v>
+        <v>0.03585348650813103</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05528902634978294</v>
+        <v>0.6085240840911865</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005879474338144064</v>
+        <v>0.1561163663864136</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02608864568173885</v>
+        <v>0.5141735076904297</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01656553521752357</v>
+        <v>0.2091945260763168</v>
       </c>
       <c r="O5" t="n">
-        <v>0.007881533354520798</v>
+        <v>0.05105598270893097</v>
       </c>
       <c r="P5" t="n">
-        <v>0.000222514383494854</v>
+        <v>0.01805300265550613</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01248343009501696</v>
+        <v>0.1704809665679932</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0008725316729396582</v>
+        <v>0.02439838275313377</v>
       </c>
       <c r="S5" t="n">
-        <v>0.006147424690425396</v>
+        <v>0.02809943072497845</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01160421874374151</v>
+        <v>0.008255394175648689</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00576552702113986</v>
+        <v>0.01795975863933563</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002347661647945642</v>
+        <v>0.01045793667435646</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003095142543315887</v>
+        <v>0.05653439089655876</v>
       </c>
       <c r="X5" t="n">
-        <v>0.007499059662222862</v>
+        <v>0.2091804593801498</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004556894302368164</v>
+        <v>0.04158801957964897</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.007153819780796766</v>
+        <v>0.02196250855922699</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.009757732041180134</v>
+        <v>0.1185841038823128</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00110962288454175</v>
+        <v>0.05635666102170944</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.005354426335543394</v>
+        <v>0.03922970592975616</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.003826997242867947</v>
+        <v>0.01287970878183842</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0001386469230055809</v>
+        <v>0.139909029006958</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.004427178762853146</v>
+        <v>0.02271461859345436</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.003818389726802707</v>
+        <v>0.004970373585820198</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.00549022015184164</v>
+        <v>0.06284130364656448</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.004594096913933754</v>
+        <v>0.03841583803296089</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.005866410210728645</v>
+        <v>0.03556670248508453</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0006462996825575829</v>
+        <v>0.02121024578809738</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01255261804908514</v>
+        <v>0.1393368691205978</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.002773266052827239</v>
+        <v>0.01507539860904217</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.00311513664200902</v>
+        <v>0.11104516685009</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.003062494099140167</v>
+        <v>0.1573378145694733</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.005118861794471741</v>
+        <v>0.08385773003101349</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.006552468053996563</v>
+        <v>0.01249335333704948</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.003009601728990674</v>
+        <v>0.04534047469496727</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.005980482790619135</v>
+        <v>0.0366496853530407</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.00603688508272171</v>
+        <v>0.02683299779891968</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.03948071226477623</v>
+        <v>0.3704270124435425</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.004887477029114962</v>
+        <v>0.03512438386678696</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.001622692681849003</v>
+        <v>0.1470510810613632</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.004003736190497875</v>
+        <v>0.126936137676239</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.001067108009010553</v>
+        <v>0.0004463391378521919</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.003227847628295422</v>
+        <v>0.02950609475374222</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.01156781520694494</v>
+        <v>0.07175774872303009</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.003679490415379405</v>
+        <v>0.005559914279729128</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0007653210777789354</v>
+        <v>0.09706331044435501</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.009477126412093639</v>
+        <v>0.1318254619836807</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.007196960505098104</v>
+        <v>0.09303371608257294</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.008505468256771564</v>
+        <v>0.03933803737163544</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.02116116136312485</v>
+        <v>0.009974358603358269</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.004839488305151463</v>
+        <v>0.210665836930275</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.001707989722490311</v>
+        <v>0.02285769581794739</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.008154215291142464</v>
+        <v>0.01401420030742884</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.003386802971363068</v>
+        <v>0.09648429602384567</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.005667921155691147</v>
+        <v>0.06760729849338531</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.002363297389820218</v>
+        <v>0.08238419145345688</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.003509841859340668</v>
+        <v>0.0241320226341486</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.002151111140847206</v>
+        <v>0.01339800097048283</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.007827384397387505</v>
+        <v>0.08295073360204697</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.006412386894226074</v>
+        <v>0.05651260167360306</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.003035072237253189</v>
+        <v>0.02595369145274162</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.004550244193524122</v>
+        <v>0.04722273722290993</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.005666847340762615</v>
+        <v>0.01061008218675852</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.004956250544637442</v>
+        <v>0.05013088136911392</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.02367058210074902</v>
+        <v>0.2250992655754089</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.001057407353073359</v>
+        <v>0.05190645158290863</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.00245203566737473</v>
+        <v>0.1488894820213318</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.004100137390196323</v>
+        <v>0.03429329395294189</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.00539189949631691</v>
+        <v>0.08039569854736328</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.00152927206363529</v>
+        <v>0.03022517822682858</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0008989582420326769</v>
+        <v>0.02062184549868107</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.008736792951822281</v>
+        <v>0.07116825133562088</v>
       </c>
       <c r="CD5" t="n">
-        <v>7.767288479954004e-05</v>
+        <v>0.03759116679430008</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.01246247068047523</v>
+        <v>0.1833287179470062</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.003484769724309444</v>
+        <v>0.04106142371892929</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.005868591833859682</v>
+        <v>0.1341378390789032</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.002245448064059019</v>
+        <v>0.01695879362523556</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.001545041101053357</v>
+        <v>0.01527899224311113</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.003660409711301327</v>
+        <v>0.004472855012863874</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.001444481662474573</v>
+        <v>0.01042472384870052</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.003196695353835821</v>
+        <v>0.007818449288606644</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.007694421336054802</v>
+        <v>0.09991998225450516</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.004612935241311789</v>
+        <v>0.1966474652290344</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.001879851333796978</v>
+        <v>0.1267984062433243</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.006451547145843506</v>
+        <v>0.1275744438171387</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.009577520191669464</v>
+        <v>0.1075319051742554</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.007150326855480671</v>
+        <v>0.05616148188710213</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.01378542184829712</v>
+        <v>0.04151396080851555</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.006796847097575665</v>
+        <v>0.04758758097887039</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0008157362462952733</v>
+        <v>0.07103990763425827</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0007344427285715938</v>
+        <v>0.02365420386195183</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.01156790181994438</v>
+        <v>0.1682831346988678</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.003885059850290418</v>
+        <v>0.03603946045041084</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.007838912308216095</v>
+        <v>0.1177120357751846</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.002362413331866264</v>
+        <v>0.0310205165296793</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.003426617477089167</v>
+        <v>0.01351860724389553</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.004617074970155954</v>
+        <v>0.008373669348657131</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0005650819512084126</v>
+        <v>0.005841079633682966</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.001707678427919745</v>
+        <v>0.023997463285923</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.006516915280371904</v>
+        <v>0.08018672466278076</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.01980389840900898</v>
+        <v>0.1414958238601685</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.004604114219546318</v>
+        <v>0.04477059468626976</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.02228866331279278</v>
+        <v>0.07826954126358032</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.005836199503391981</v>
+        <v>0.09919301420450211</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.003531018039211631</v>
+        <v>0.09733259677886963</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.001393932150676847</v>
+        <v>0.03501585870981216</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.007673375308513641</v>
+        <v>0.1749393790960312</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.001771322800777853</v>
+        <v>0.007540830411016941</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.001641172799281776</v>
+        <v>0.02174453437328339</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.003154839621856809</v>
+        <v>0.1228684857487679</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.004720894154161215</v>
+        <v>0.04681730270385742</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.000914489442948252</v>
+        <v>0.08630123734474182</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.001879142364487052</v>
+        <v>0.01267072558403015</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.00431352062150836</v>
+        <v>0.01125343516469002</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0004773078253492713</v>
+        <v>0.08132198452949524</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0003517367586027831</v>
+        <v>0.01322936825454235</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.009152866899967194</v>
+        <v>0.1180348694324493</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.00254042143933475</v>
+        <v>0.03473532199859619</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.008029939606785774</v>
+        <v>0.002222003415226936</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.004671524278819561</v>
+        <v>0.00117498729377985</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.006673608440905809</v>
+        <v>0.1401920169591904</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0006247408455237746</v>
+        <v>0.1032957881689072</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.00530829094350338</v>
+        <v>0.004473425913602114</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0002575934049673378</v>
+        <v>0.007541237398982048</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.001997237326577306</v>
+        <v>0.1712244749069214</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.003133623860776424</v>
+        <v>0.1055307164788246</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.00463664997369051</v>
+        <v>0.04865391179919243</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.01055418979376554</v>
+        <v>0.1537269055843353</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.00255618873052299</v>
+        <v>0.01340798940509558</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.001711981487460434</v>
+        <v>0.07589944452047348</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.004833333194255829</v>
+        <v>0.07778677344322205</v>
       </c>
       <c r="EK5" t="n">
-        <v>1.731474185362458e-05</v>
+        <v>0.007089514285326004</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.001239049015566707</v>
+        <v>0.004627508111298084</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.002946597523987293</v>
+        <v>0.01639031246304512</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.001041013048961759</v>
+        <v>0.007420117035508156</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.002052271272987127</v>
+        <v>0.05012533813714981</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.009268426336348057</v>
+        <v>0.0421418771147728</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.008857267908751965</v>
+        <v>0.05233822390437126</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.004824222065508366</v>
+        <v>0.005252953618764877</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.007208077237010002</v>
+        <v>0.01397379953414202</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.00807921402156353</v>
+        <v>0.04432540759444237</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.007052627392113209</v>
+        <v>0.05346616730093956</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.002933325013145804</v>
+        <v>0.04354159161448479</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.002136789727956057</v>
+        <v>0.0514388419687748</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0002441643737256527</v>
+        <v>0.04920386523008347</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.01322517544031143</v>
+        <v>0.1922926604747772</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.003504937514662743</v>
+        <v>0.03189156204462051</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.006904867477715015</v>
+        <v>0.1433168947696686</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.002633726224303246</v>
+        <v>0.00923356506973505</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.004235505126416683</v>
+        <v>0.0007947022095322609</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.004133885260671377</v>
+        <v>0.008502021431922913</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0005506914458237588</v>
+        <v>0.0269226860255003</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.002838357351720333</v>
+        <v>0.01826687902212143</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0005376485642045736</v>
+        <v>0.02038713172078133</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.007507521659135818</v>
+        <v>0.1109765097498894</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.009387754835188389</v>
+        <v>0.1132097542285919</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.002568704774603248</v>
+        <v>0.05604473873972893</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.001050184830091894</v>
+        <v>0.1155391186475754</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0003100035828538239</v>
+        <v>0.0316101498901844</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.002596226520836353</v>
+        <v>0.008441414684057236</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.001702851965092123</v>
+        <v>0.1348121464252472</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.004162210505455732</v>
+        <v>0.07498575747013092</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.0007916619069874287</v>
+        <v>0.05226000398397446</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.001038236310705543</v>
+        <v>0.1877170652151108</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.02225127071142197</v>
+        <v>0.06270831078290939</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.003259345889091492</v>
+        <v>0.1595991253852844</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.007037504576146603</v>
+        <v>0.07414573431015015</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.001757366582751274</v>
+        <v>0.06469722092151642</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.002295991871505976</v>
+        <v>0.001842052675783634</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.003617269918322563</v>
+        <v>0.1121552884578705</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.00266483798623085</v>
+        <v>0.1149938330054283</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.005530954338610172</v>
+        <v>0.04796651750802994</v>
       </c>
       <c r="FZ5" t="n">
-        <v>9.852289804257452e-05</v>
+        <v>0.1687270104885101</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0005544214509427547</v>
+        <v>0.02918654680252075</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.002431507455185056</v>
+        <v>0.1073399409651756</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.01429883949458599</v>
+        <v>0.2480622231960297</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.008926344104111195</v>
+        <v>0.03450896590948105</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.01914030499756336</v>
+        <v>0.2139194011688232</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.002914067823439837</v>
+        <v>0.0272575318813324</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.01251828018575907</v>
+        <v>0.02137196995317936</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0003696922212839127</v>
+        <v>0.1692173182964325</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1935181319713593</v>
+        <v>0.7735849618911743</v>
       </c>
       <c r="C6" t="n">
-        <v>0.005874425172805786</v>
+        <v>0.1468551605939865</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01082772016525269</v>
+        <v>0.1790724545717239</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0368480496108532</v>
+        <v>0.1454841941595078</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0381549671292305</v>
+        <v>0.4724490642547607</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008535310626029968</v>
+        <v>0.02969425171613693</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008183344267308712</v>
+        <v>0.09432826936244965</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03113594651222229</v>
+        <v>0.102160856127739</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0267026275396347</v>
+        <v>0.1176745817065239</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1229685544967651</v>
+        <v>0.8908275365829468</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009381286799907684</v>
+        <v>0.2145413160324097</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02075548842549324</v>
+        <v>0.3074586093425751</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02334645017981529</v>
+        <v>0.001765675842761993</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04769944399595261</v>
+        <v>0.3705737292766571</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02335566096007824</v>
+        <v>0.01957909017801285</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02661623805761337</v>
+        <v>0.07305002212524414</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0289952028542757</v>
+        <v>0.07919684052467346</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01516614481806755</v>
+        <v>0.03141496703028679</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04126114025712013</v>
+        <v>0.05913694947957993</v>
       </c>
       <c r="U6" t="n">
-        <v>0.008006235584616661</v>
+        <v>0.02080339938402176</v>
       </c>
       <c r="V6" t="n">
-        <v>0.006072414107620716</v>
+        <v>0.1144708544015884</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02888399176299572</v>
+        <v>0.112489715218544</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01858178153634071</v>
+        <v>0.09997915476560593</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0304238386452198</v>
+        <v>0.009691717103123665</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03833552449941635</v>
+        <v>0.05727060884237289</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001124897738918662</v>
+        <v>0.1117470487952232</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.02270369045436382</v>
+        <v>0.1769112646579742</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.07037051767110825</v>
+        <v>0.03367383778095245</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.01806642301380634</v>
+        <v>0.00957915373146534</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0001315739937126637</v>
+        <v>0.2888566851615906</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.00330507243052125</v>
+        <v>0.1927361935377121</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.00840454176068306</v>
+        <v>0.009655836969614029</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.003053978085517883</v>
+        <v>0.09977351129055023</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.02725490182638168</v>
+        <v>0.1056823134422302</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.002804005984216928</v>
+        <v>0.002188113518059254</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.02790369838476181</v>
+        <v>0.04470374435186386</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.03333240002393723</v>
+        <v>0.1124683022499084</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.007709682919085026</v>
+        <v>0.03751818463206291</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.02669817022979259</v>
+        <v>0.06395580619573593</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.02332028560340405</v>
+        <v>0.008083999156951904</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.03909509256482124</v>
+        <v>0.06381615996360779</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.01243634056299925</v>
+        <v>0.08235498517751694</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.01915367506444454</v>
+        <v>0.05395692586898804</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.01043823920190334</v>
+        <v>0.07818780839443207</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.02424724400043488</v>
+        <v>0.172410786151886</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1671106815338135</v>
+        <v>0.6357927918434143</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.004017342813313007</v>
+        <v>0.04471606761217117</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.01711366325616837</v>
+        <v>0.100691631436348</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.02815933711826801</v>
+        <v>0.2977475225925446</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.02346649207174778</v>
+        <v>0.1813107430934906</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.02510479465126991</v>
+        <v>0.005694584921002388</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.005814380943775177</v>
+        <v>0.04853743314743042</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.008684000000357628</v>
+        <v>0.04633599892258644</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.004366816021502018</v>
+        <v>0.07210804522037506</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0312834195792675</v>
+        <v>0.0353146530687809</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.04305630549788475</v>
+        <v>0.09772467613220215</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.05450957268476486</v>
+        <v>0.1803891211748123</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.0326300822198391</v>
+        <v>0.1457734853029251</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.002430793363600969</v>
+        <v>0.1859813928604126</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0009555788710713387</v>
+        <v>0.08790241926908493</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.02334056422114372</v>
+        <v>0.1235205009579659</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.02332703769207001</v>
+        <v>0.09573332220315933</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.01542074978351593</v>
+        <v>0.05349058657884598</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.07975973188877106</v>
+        <v>0.09469296038150787</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.01251120399683714</v>
+        <v>0.05987393483519554</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.03811405971646309</v>
+        <v>0.07741525769233704</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.06448140740394592</v>
+        <v>0.0005873367190361023</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.03620551154017448</v>
+        <v>0.02486274018883705</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.02914658933877945</v>
+        <v>0.1820482015609741</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.02200173400342464</v>
+        <v>0.01071686577051878</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.008314867503941059</v>
+        <v>0.04749852418899536</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.01214021537452936</v>
+        <v>0.05349745601415634</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.08479755371809006</v>
+        <v>0.2229852080345154</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.03818647190928459</v>
+        <v>0.07147228717803955</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.01248357817530632</v>
+        <v>0.09739142656326294</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.004182510077953339</v>
+        <v>0.1315756142139435</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.00615636445581913</v>
+        <v>0.2069148570299149</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.02447072044014931</v>
+        <v>0.01787354052066803</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.001142680761404335</v>
+        <v>0.01160171534866095</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.01332242507487535</v>
+        <v>0.04180977866053581</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.006936769932508469</v>
+        <v>0.01325902435928583</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.02715646848082542</v>
+        <v>0.214943990111351</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.007048023398965597</v>
+        <v>0.07164782285690308</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.01394209638237953</v>
+        <v>0.05319979786872864</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0003195086610503495</v>
+        <v>0.01125011499971151</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.0002556926046963781</v>
+        <v>0.09756637364625931</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.0001871460117399693</v>
+        <v>0.03689894080162048</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.005551057402044535</v>
+        <v>0.03543329238891602</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.004415906500071287</v>
+        <v>0.03482624515891075</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.03272397816181183</v>
+        <v>0.04697903990745544</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.04700258746743202</v>
+        <v>0.08618280291557312</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.0156020475551486</v>
+        <v>0.1532412767410278</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.03219015896320343</v>
+        <v>0.2479848563671112</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.007343011908233166</v>
+        <v>0.1910758912563324</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.0420919805765152</v>
+        <v>0.1645221263170242</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.03068992309272289</v>
+        <v>0.03863541036844254</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.005882739089429379</v>
+        <v>0.06813165545463562</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.005411393474787474</v>
+        <v>0.01601759344339371</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.001670547062531114</v>
+        <v>0.05001742020249367</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.02175465039908886</v>
+        <v>0.2055379152297974</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.01590395905077457</v>
+        <v>0.0643233135342598</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.01844064891338348</v>
+        <v>0.05994437262415886</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.001911174273118377</v>
+        <v>0.01566336303949356</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.009624263271689415</v>
+        <v>0.1133797764778137</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0007896487368270755</v>
+        <v>0.02308458462357521</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.005060271359980106</v>
+        <v>0.02770698070526123</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.002939110854640603</v>
+        <v>0.02782440558075905</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.02514100819826126</v>
+        <v>0.1052548438310623</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.0784635990858078</v>
+        <v>0.09212189912796021</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.00682289432734251</v>
+        <v>0.02214042097330093</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.05651811882853508</v>
+        <v>0.08249965310096741</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.06822190433740616</v>
+        <v>0.1294989436864853</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.04478330165147781</v>
+        <v>0.1929392367601395</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.06070902571082115</v>
+        <v>0.02751120366156101</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.01500988285988569</v>
+        <v>0.06196010857820511</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.01876197010278702</v>
+        <v>0.09542586654424667</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.0004130657762289047</v>
+        <v>0.08166249096393585</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.02067925594747066</v>
+        <v>0.03033345006406307</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.00698262732475996</v>
+        <v>0.06630399823188782</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.03007834032177925</v>
+        <v>0.01762740314006805</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.07270979881286621</v>
+        <v>0.1593406200408936</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.008376339450478554</v>
+        <v>0.02926565334200859</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.02173382416367531</v>
+        <v>0.05465338006615639</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.01879189722239971</v>
+        <v>0.1416163146495819</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.01477333437651396</v>
+        <v>0.01195092685520649</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.000256129598710686</v>
+        <v>0.04669702798128128</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.01790177449584007</v>
+        <v>0.02518082410097122</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.03382525220513344</v>
+        <v>0.08413562178611755</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.01715544797480106</v>
+        <v>0.1409307867288589</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.02028478309512138</v>
+        <v>0.02130474708974361</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.002637454075738788</v>
+        <v>0.05683799088001251</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.009688698686659336</v>
+        <v>0.01615010388195515</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.03960520401597023</v>
+        <v>0.08899299055337906</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.008687993511557579</v>
+        <v>0.05740068852901459</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.006002216599881649</v>
+        <v>0.02118869870901108</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.005021429155021906</v>
+        <v>0.125172346830368</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.005052597727626562</v>
+        <v>0.007616376504302025</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.002309720264747739</v>
+        <v>0.05643865838646889</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.005891146138310432</v>
+        <v>0.0590827539563179</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.008314921520650387</v>
+        <v>0.06189717352390289</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.004318525083363056</v>
+        <v>0.03992980718612671</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.01319317705929279</v>
+        <v>0.006747599225491285</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.003175541758537292</v>
+        <v>0.006362718529999256</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.01452502328902483</v>
+        <v>0.04570044577121735</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.03190336003899574</v>
+        <v>0.1414996534585953</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.01987681351602077</v>
+        <v>0.09871582686901093</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.02815284207463264</v>
+        <v>0.02810751646757126</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.0307730995118618</v>
+        <v>0.06506219506263733</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.02346027456223965</v>
+        <v>0.08004133403301239</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.01956732012331486</v>
+        <v>0.006734760012477636</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.04952407628297806</v>
+        <v>0.02723308093845844</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.001082235015928745</v>
+        <v>0.01234440132975578</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.007433197926729918</v>
+        <v>0.02257806435227394</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.02017149701714516</v>
+        <v>0.2335618287324905</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.00933025311678648</v>
+        <v>0.06023415178060532</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.01015225425362587</v>
+        <v>0.06249528378248215</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.006920317187905312</v>
+        <v>0.05458375811576843</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.01296058110892773</v>
+        <v>0.09729737043380737</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.002173359273001552</v>
+        <v>0.04473574832081795</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.0006113043637014925</v>
+        <v>0.04047227650880814</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.005179138854146004</v>
+        <v>0.0131481634452939</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.02133041247725487</v>
+        <v>0.01138169132173061</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.009750183671712875</v>
+        <v>0.2257141172885895</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.02114727720618248</v>
+        <v>0.09468755125999451</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.008230039849877357</v>
+        <v>0.03163718432188034</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.05358953401446342</v>
+        <v>0.1440370231866837</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.02140921540558338</v>
+        <v>0.1461597234010696</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.0102014048025012</v>
+        <v>0.1080407649278641</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.04391878843307495</v>
+        <v>0.09938259422779083</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.01212313584983349</v>
+        <v>0.09291744977235794</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.003984660841524601</v>
+        <v>0.001646429300308228</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.00596508476883173</v>
+        <v>0.1390057653188705</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.0321381650865078</v>
+        <v>0.1187071800231934</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.03198833018541336</v>
+        <v>0.1840047836303711</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.05686276778578758</v>
+        <v>0.01102491561323404</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.006906546652317047</v>
+        <v>0.07907295227050781</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.01699850894510746</v>
+        <v>0.04574013501405716</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.01097536087036133</v>
+        <v>0.04833848401904106</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.01760410331189632</v>
+        <v>0.04324078559875488</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.04913304001092911</v>
+        <v>0.1250413358211517</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.001336706685833633</v>
+        <v>0.06400216370820999</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.03373020887374878</v>
+        <v>0.2357481867074966</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.02405979111790657</v>
+        <v>0.003159664338454604</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.08452510833740234</v>
+        <v>0.1392601430416107</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0391676053404808</v>
+        <v>0.1250776499509811</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.05782521516084671</v>
+        <v>0.04740174859762192</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.0153767429292202</v>
+        <v>0.04738824814558029</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.001649610232561827</v>
+        <v>0.0447484515607357</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.06099121645092964</v>
+        <v>0.09051670134067535</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3009279072284698</v>
+        <v>0.8035866022109985</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07685284316539764</v>
+        <v>0.1014493927359581</v>
       </c>
       <c r="D7" t="n">
-        <v>0.441862165927887</v>
+        <v>0.7290424704551697</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1602681577205658</v>
+        <v>0.08785669505596161</v>
       </c>
       <c r="F7" t="n">
-        <v>0.12230534106493</v>
+        <v>0.2153039127588272</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09883236140012741</v>
+        <v>0.4094835221767426</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06125263124704361</v>
+        <v>0.09359022229909897</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07357059419155121</v>
+        <v>0.09382571280002594</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1283983141183853</v>
+        <v>0.1211662590503693</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2616273462772369</v>
+        <v>0.7360453605651855</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06068385764956474</v>
+        <v>0.1749133169651031</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3574462234973907</v>
+        <v>0.986469566822052</v>
       </c>
       <c r="N7" t="n">
-        <v>0.08700840175151825</v>
+        <v>0.2215372622013092</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1193302348256111</v>
+        <v>0.02045730128884315</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0680781677365303</v>
+        <v>0.3261464834213257</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.08288884907960892</v>
+        <v>0.1448777168989182</v>
       </c>
       <c r="R7" t="n">
-        <v>0.07044190168380737</v>
+        <v>0.002764977514743805</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01759654842317104</v>
+        <v>0.03888970613479614</v>
       </c>
       <c r="T7" t="n">
-        <v>0.05508698523044586</v>
+        <v>0.06878159940242767</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0598490945994854</v>
+        <v>0.06122124940156937</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1560093462467194</v>
+        <v>0.01682228781282902</v>
       </c>
       <c r="W7" t="n">
-        <v>0.02156044542789459</v>
+        <v>0.05537459999322891</v>
       </c>
       <c r="X7" t="n">
-        <v>0.09231686592102051</v>
+        <v>0.1899578273296356</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002488860860466957</v>
+        <v>0.06487510353326797</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01508344709873199</v>
+        <v>0.06878233700990677</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02449474483728409</v>
+        <v>0.1618754714727402</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01245679892599583</v>
+        <v>0.02703109383583069</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.02318800985813141</v>
+        <v>0.04285066574811935</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.01862013712525368</v>
+        <v>0.05292023718357086</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.02368940412998199</v>
+        <v>0.1101883500814438</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.01953506469726562</v>
+        <v>0.09191359579563141</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0203841794282198</v>
+        <v>0.04520959034562111</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.005702894181013107</v>
+        <v>0.006922446191310883</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.01912424899637699</v>
+        <v>0.1026958003640175</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.08068130165338516</v>
+        <v>0.0288532804697752</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.03199102729558945</v>
+        <v>0.1063749641180038</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.04666566848754883</v>
+        <v>0.2514432072639465</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.04475196450948715</v>
+        <v>0.003981452435255051</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.01589140668511391</v>
+        <v>0.1054506450891495</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.03799095749855042</v>
+        <v>0.305826723575592</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.03309713676571846</v>
+        <v>0.1347708851099014</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0001397714950144291</v>
+        <v>0.01075155287981033</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.01849505864083767</v>
+        <v>0.07163906842470169</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.07109791040420532</v>
+        <v>0.05036436766386032</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.004850168246775866</v>
+        <v>0.1245497986674309</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.07589706033468246</v>
+        <v>0.5226082801818848</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.05535503476858139</v>
+        <v>0.1253627091646194</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.1906609386205673</v>
+        <v>0.4174672961235046</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1481070965528488</v>
+        <v>0.2883638143539429</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.07369224727153778</v>
+        <v>0.02483894862234592</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.02424667961895466</v>
+        <v>0.06675657629966736</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.02802122011780739</v>
+        <v>0.03508462756872177</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.1009436175227165</v>
+        <v>0.01971404254436493</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.06847693026065826</v>
+        <v>0.123510517179966</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.1116891652345657</v>
+        <v>0.04212108999490738</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.1046894118189812</v>
+        <v>0.1497704237699509</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.1465325057506561</v>
+        <v>0.07771307975053787</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.0217909924685955</v>
+        <v>0.03686783835291862</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.03430239111185074</v>
+        <v>0.1297296434640884</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.01890138909220695</v>
+        <v>0.2127360105514526</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.1085967943072319</v>
+        <v>0.07569228112697601</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.05139745026826859</v>
+        <v>0.1939728856086731</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.04980221390724182</v>
+        <v>0.06618981808423996</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.05157315731048584</v>
+        <v>0.1744877398014069</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.06013777479529381</v>
+        <v>0.009628755040466785</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.001176755875349045</v>
+        <v>0.04207980632781982</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.02389921993017197</v>
+        <v>0.06472982466220856</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.03222233057022095</v>
+        <v>0.03718193247914314</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.01297593116760254</v>
+        <v>0.03423899412155151</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.019599549472332</v>
+        <v>0.1219584792852402</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.006590311415493488</v>
+        <v>0.06710087507963181</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.06628721952438354</v>
+        <v>0.09508266299962997</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.05036963522434235</v>
+        <v>0.3008245527744293</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0779738575220108</v>
+        <v>0.03404287621378899</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.1243498101830482</v>
+        <v>0.3917350769042969</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.02652934566140175</v>
+        <v>0.0545327216386795</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.004732538945972919</v>
+        <v>0.1169206649065018</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.02032147720456123</v>
+        <v>0.04642514511942863</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.03683324530720711</v>
+        <v>0.05387930944561958</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.07368654012680054</v>
+        <v>0.1303673088550568</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0202799029648304</v>
+        <v>0.05383544415235519</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.02830827981233597</v>
+        <v>0.2288572788238525</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.04141403362154961</v>
+        <v>0.04922471940517426</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.08291996270418167</v>
+        <v>0.2751157283782959</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.03280430659651756</v>
+        <v>0.02333510294556618</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.03130174428224564</v>
+        <v>0.001288409344851971</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.000975314062088728</v>
+        <v>0.0003953231498599052</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.004874546080827713</v>
+        <v>0.01482479274272919</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0324028953909874</v>
+        <v>0.05202632397413254</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.01465503498911858</v>
+        <v>0.06030088290572166</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.07334983348846436</v>
+        <v>0.1133609563112259</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.02355999127030373</v>
+        <v>0.119774118065834</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.01235258486121893</v>
+        <v>0.3657452464103699</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.02631090581417084</v>
+        <v>0.07081303745508194</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.002941161394119263</v>
+        <v>0.01433834992349148</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.1027486175298691</v>
+        <v>0.02604946494102478</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.002161263488233089</v>
+        <v>0.0341351181268692</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.01114086993038654</v>
+        <v>0.1594501882791519</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.02473743259906769</v>
+        <v>0.0463702529668808</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.04008697718381882</v>
+        <v>0.2214311808347702</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.03969110921025276</v>
+        <v>0.05182866752147675</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.07619287073612213</v>
+        <v>0.2573632597923279</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.03971206396818161</v>
+        <v>0.009838534519076347</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.02887280285358429</v>
+        <v>0.004583508707582951</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.01600592397153378</v>
+        <v>0.002407874912023544</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.005830345675349236</v>
+        <v>0.003737782128155231</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.01722041144967079</v>
+        <v>0.06737561523914337</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.02363600023090839</v>
+        <v>0.02289669215679169</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.07464682310819626</v>
+        <v>0.2738598585128784</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.01125708501785994</v>
+        <v>0.002708841115236282</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.1190830543637276</v>
+        <v>0.1509186327457428</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.02756930328905582</v>
+        <v>0.1367078125476837</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.05392241850495338</v>
+        <v>0.2155210375785828</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.07479703426361084</v>
+        <v>0.1416457891464233</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.05960524454712868</v>
+        <v>0.3646404445171356</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.09171167761087418</v>
+        <v>0.008565777912735939</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.004223149735480547</v>
+        <v>0.01244215667247772</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.02677569910883904</v>
+        <v>0.1195919290184975</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.01962029561400414</v>
+        <v>0.03167769685387611</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.06171508505940437</v>
+        <v>0.1574723422527313</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.05439935624599457</v>
+        <v>0.03496134281158447</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.01844526827335358</v>
+        <v>0.04351348057389259</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.01116343587636948</v>
+        <v>0.1321671009063721</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.03644013404846191</v>
+        <v>0.08771494776010513</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.06172496452927589</v>
+        <v>0.2698977589607239</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.02605355903506279</v>
+        <v>0.02654866129159927</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0004735160619020462</v>
+        <v>0.01113628596067429</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.007958901114761829</v>
+        <v>0.04655660688877106</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.03457897529006004</v>
+        <v>0.06601785123348236</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.03328078985214233</v>
+        <v>0.007387562654912472</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.007439963985234499</v>
+        <v>0.004461687989532948</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.01779357716441154</v>
+        <v>0.06833211332559586</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.01689958013594151</v>
+        <v>0.187323197722435</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.002746247919276357</v>
+        <v>0.2742727398872375</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0004050694406032562</v>
+        <v>0.04687661305069923</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.03722966089844704</v>
+        <v>0.225308820605278</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.04230890423059464</v>
+        <v>0.02209042757749557</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.02166296914219856</v>
+        <v>0.2336545437574387</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.001291206106543541</v>
+        <v>0.1035000383853912</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.05453707650303841</v>
+        <v>0.03678270056843758</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.01112580392509699</v>
+        <v>0.01333743892610073</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.02583914250135422</v>
+        <v>0.001718097133561969</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.01455349009484053</v>
+        <v>0.0210595615208149</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.07077334821224213</v>
+        <v>0.05990348756313324</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.003079491667449474</v>
+        <v>0.08896155655384064</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.04048744589090347</v>
+        <v>0.02279403433203697</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.03158019110560417</v>
+        <v>0.1703015863895416</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.0009615563903935254</v>
+        <v>0.02502007409930229</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.07305572926998138</v>
+        <v>0.05504213646054268</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.05188968777656555</v>
+        <v>0.02523740381002426</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.09796773642301559</v>
+        <v>0.09239691495895386</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.02118225023150444</v>
+        <v>0.1182100996375084</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0192621573805809</v>
+        <v>0.05099755525588989</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.02477523125708103</v>
+        <v>0.2424448728561401</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.03644734621047974</v>
+        <v>0.04918283596634865</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.08090298622846603</v>
+        <v>0.3077020645141602</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.02625646442174911</v>
+        <v>0.01454737689346075</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.02528399601578712</v>
+        <v>0.02538242191076279</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.01326534803956747</v>
+        <v>0.009256914258003235</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.005832890048623085</v>
+        <v>0.02668287605047226</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.03496003150939941</v>
+        <v>0.06783656030893326</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0682695284485817</v>
+        <v>0.05169344693422318</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.02067949995398521</v>
+        <v>0.149472713470459</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.009627493098378181</v>
+        <v>0.1984795182943344</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.03265638276934624</v>
+        <v>0.1286284476518631</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.06321989744901657</v>
+        <v>0.1476142406463623</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.01865064539015293</v>
+        <v>0.02591440454125404</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.005840005353093147</v>
+        <v>0.004122540354728699</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.04939163848757744</v>
+        <v>0.0211503691971302</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.008861348032951355</v>
+        <v>0.1491625159978867</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.01254912093281746</v>
+        <v>0.04557640478014946</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.02789097279310226</v>
+        <v>0.2674145996570587</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.01899915374815464</v>
+        <v>0.1022223830223083</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.05998553335666656</v>
+        <v>0.4833968579769135</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.08135441690683365</v>
+        <v>0.02488239109516144</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.05987736210227013</v>
+        <v>0.1052810177206993</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.08617735654115677</v>
+        <v>0.007738303393125534</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.01449335739016533</v>
+        <v>0.04649430513381958</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.01511470228433609</v>
+        <v>0.1975496113300323</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.03146705776453018</v>
+        <v>0.1211013942956924</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.07354013621807098</v>
+        <v>0.149660512804985</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.01494030095636845</v>
+        <v>0.09403455257415771</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.02175787091255188</v>
+        <v>0.1269121468067169</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.0154338339343667</v>
+        <v>0.3475011885166168</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.02770235575735569</v>
+        <v>0.02634123712778091</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.1861947029829025</v>
+        <v>0.2643133103847504</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.07414332777261734</v>
+        <v>0.09000250697135925</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.02986739948391914</v>
+        <v>0.02213799394667149</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5.815768489014772e-08</v>
+        <v>0.02147721871733665</v>
       </c>
       <c r="B8" t="n">
-        <v>1.216781253532417e-08</v>
+        <v>0.5228889584541321</v>
       </c>
       <c r="C8" t="n">
-        <v>3.794113823119005e-08</v>
+        <v>0.001937426626682281</v>
       </c>
       <c r="D8" t="n">
-        <v>6.649678141457116e-08</v>
+        <v>0.4969701170921326</v>
       </c>
       <c r="E8" t="n">
-        <v>6.025196341852279e-09</v>
+        <v>0.007624763064086437</v>
       </c>
       <c r="F8" t="n">
-        <v>2.013098310271744e-08</v>
+        <v>0.3288636207580566</v>
       </c>
       <c r="G8" t="n">
-        <v>6.320654222236044e-09</v>
+        <v>0.1358901560306549</v>
       </c>
       <c r="H8" t="n">
-        <v>2.229749895832356e-08</v>
+        <v>0.2382462918758392</v>
       </c>
       <c r="I8" t="n">
-        <v>4.074508908047392e-08</v>
+        <v>0.03221365064382553</v>
       </c>
       <c r="J8" t="n">
-        <v>3.632607104009367e-08</v>
+        <v>0.1218144148588181</v>
       </c>
       <c r="K8" t="n">
-        <v>4.819287724444621e-08</v>
+        <v>0.495389461517334</v>
       </c>
       <c r="L8" t="n">
-        <v>3.126959313703992e-08</v>
+        <v>0.09784435480833054</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09787308133491e-08</v>
+        <v>0.6144477725028992</v>
       </c>
       <c r="N8" t="n">
-        <v>2.646793006988446e-08</v>
+        <v>0.04719763249158859</v>
       </c>
       <c r="O8" t="n">
-        <v>5.923946133634672e-08</v>
+        <v>0.3875577449798584</v>
       </c>
       <c r="P8" t="n">
-        <v>4.502511252724162e-09</v>
+        <v>0.2069880068302155</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.596259029985504e-08</v>
+        <v>0.1283244043588638</v>
       </c>
       <c r="R8" t="n">
-        <v>1.645154945606464e-08</v>
+        <v>0.01058395020663738</v>
       </c>
       <c r="S8" t="n">
-        <v>1.086654677351362e-08</v>
+        <v>0.07180123031139374</v>
       </c>
       <c r="T8" t="n">
-        <v>1.363301382895088e-08</v>
+        <v>0.02231532149016857</v>
       </c>
       <c r="U8" t="n">
-        <v>1.728046861160237e-08</v>
+        <v>0.06257138401269913</v>
       </c>
       <c r="V8" t="n">
-        <v>2.321274195082879e-08</v>
+        <v>0.05308340489864349</v>
       </c>
       <c r="W8" t="n">
-        <v>7.976385063557245e-08</v>
+        <v>0.1307877600193024</v>
       </c>
       <c r="X8" t="n">
-        <v>1.471506805295064e-09</v>
+        <v>0.03448422625660896</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.440168683255251e-08</v>
+        <v>0.04742668941617012</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.381408847895727e-08</v>
+        <v>0.07424324750900269</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.43943327152374e-08</v>
+        <v>0.02439302578568459</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.297725173633808e-09</v>
+        <v>0.0392557792365551</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.16498197755277e-08</v>
+        <v>0.2054449915885925</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.800267490636998e-08</v>
+        <v>0.06633485853672028</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.90769728902751e-08</v>
+        <v>0.01345270872116089</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.479216026391896e-09</v>
+        <v>0.1102151274681091</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.311129859184803e-08</v>
+        <v>0.03964121267199516</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.527014864028843e-08</v>
+        <v>0.007235657423734665</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.009670214102698e-08</v>
+        <v>0.09901905804872513</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.827211981719756e-08</v>
+        <v>0.0463920496404171</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.669266668282489e-09</v>
+        <v>0.09512891620397568</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.193950621176555e-08</v>
+        <v>0.08987116813659668</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.174429963337388e-08</v>
+        <v>0.1091004014015198</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.647938141502436e-08</v>
+        <v>0.2266702353954315</v>
       </c>
       <c r="AO8" t="n">
-        <v>2.347031902161234e-08</v>
+        <v>0.04627799615263939</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.506021111794212e-10</v>
+        <v>0.03351519256830215</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.409625079115358e-09</v>
+        <v>0.0005226433277130127</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.558841589144322e-08</v>
+        <v>0.01575640775263309</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.01421176907013e-09</v>
+        <v>0.009223544970154762</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.280081509326465e-09</v>
+        <v>0.03223796933889389</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.895374493609552e-09</v>
+        <v>0.3740076422691345</v>
       </c>
       <c r="AV8" t="n">
-        <v>8.395733885890877e-09</v>
+        <v>0.01566211506724358</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.584184137319426e-08</v>
+        <v>0.3712064623832703</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.157587981026609e-08</v>
+        <v>0.2261778861284256</v>
       </c>
       <c r="AY8" t="n">
-        <v>2.82788441552384e-08</v>
+        <v>0.1528057605028152</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.149340426806702e-08</v>
+        <v>0.01586902886629105</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.776340460452502e-09</v>
+        <v>0.008405709639191628</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.761930766899013e-09</v>
+        <v>0.05734366923570633</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.52391609226288e-08</v>
+        <v>0.09283812344074249</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.53927021023992e-08</v>
+        <v>0.05280615016818047</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.866068709612591e-08</v>
+        <v>0.04423090070486069</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.988735753855053e-08</v>
+        <v>0.08997596800327301</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.60416541664199e-08</v>
+        <v>0.1198009997606277</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.407268695492348e-08</v>
+        <v>0.05599784478545189</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.398599008301971e-08</v>
+        <v>0.05735919252038002</v>
       </c>
       <c r="BJ8" t="n">
-        <v>4.172434842075745e-08</v>
+        <v>0.187599703669548</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.357090617659651e-08</v>
+        <v>0.08883942663669586</v>
       </c>
       <c r="BL8" t="n">
-        <v>2.270201981957598e-08</v>
+        <v>0.03159818798303604</v>
       </c>
       <c r="BM8" t="n">
-        <v>2.447070457378686e-08</v>
+        <v>0.0467713437974453</v>
       </c>
       <c r="BN8" t="n">
-        <v>9.421757596328462e-09</v>
+        <v>0.05390588194131851</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.047540625937927e-08</v>
+        <v>0.003489507362246513</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.224625538284954e-09</v>
+        <v>0.1074639409780502</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.82397027773618e-09</v>
+        <v>0.008964488282799721</v>
       </c>
       <c r="BR8" t="n">
-        <v>4.636917516620542e-09</v>
+        <v>0.02373610809445381</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.621820899799786e-08</v>
+        <v>0.06278224289417267</v>
       </c>
       <c r="BT8" t="n">
-        <v>4.405594999923323e-09</v>
+        <v>0.004098355304449797</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.044132768081909e-08</v>
+        <v>0.04542824998497963</v>
       </c>
       <c r="BV8" t="n">
-        <v>9.4577190523637e-09</v>
+        <v>0.08296938985586166</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.783810077427006e-08</v>
+        <v>0.03421966731548309</v>
       </c>
       <c r="BX8" t="n">
-        <v>5.311174611222214e-09</v>
+        <v>0.2573526501655579</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.180223208052666e-08</v>
+        <v>0.03109061904251575</v>
       </c>
       <c r="BZ8" t="n">
-        <v>5.155406768153625e-09</v>
+        <v>0.08859217911958694</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.927001314072641e-08</v>
+        <v>0.05704106390476227</v>
       </c>
       <c r="CB8" t="n">
-        <v>2.120455810938893e-08</v>
+        <v>0.05280937999486923</v>
       </c>
       <c r="CC8" t="n">
-        <v>1.345528133356311e-08</v>
+        <v>0.006846163421869278</v>
       </c>
       <c r="CD8" t="n">
-        <v>1.144791461626937e-08</v>
+        <v>0.02942611090838909</v>
       </c>
       <c r="CE8" t="n">
-        <v>4.085437543821513e-10</v>
+        <v>0.151957243680954</v>
       </c>
       <c r="CF8" t="n">
-        <v>8.222918346234565e-09</v>
+        <v>0.01988800056278706</v>
       </c>
       <c r="CG8" t="n">
-        <v>9.420556557060422e-10</v>
+        <v>0.1680939942598343</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.257803461385265e-08</v>
+        <v>0.002992961090058088</v>
       </c>
       <c r="CI8" t="n">
-        <v>8.039069854248737e-09</v>
+        <v>0.04760884866118431</v>
       </c>
       <c r="CJ8" t="n">
-        <v>4.921820284664591e-09</v>
+        <v>0.01549266651272774</v>
       </c>
       <c r="CK8" t="n">
-        <v>6.661221796377959e-09</v>
+        <v>0.03941802680492401</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.624684387024899e-08</v>
+        <v>0.007274375297129154</v>
       </c>
       <c r="CM8" t="n">
-        <v>3.325873976223193e-08</v>
+        <v>0.06460803747177124</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.002874139288679e-08</v>
+        <v>0.08597803115844727</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.251666059687295e-08</v>
+        <v>0.1041385605931282</v>
       </c>
       <c r="CP8" t="n">
-        <v>4.536350672879053e-08</v>
+        <v>0.1705590486526489</v>
       </c>
       <c r="CQ8" t="n">
-        <v>5.440344708063094e-08</v>
+        <v>0.0185496062040329</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.267601845711397e-08</v>
+        <v>0.04867550358176231</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.778959640181711e-08</v>
+        <v>0.005135519430041313</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.682150406802975e-08</v>
+        <v>0.1613209545612335</v>
       </c>
       <c r="CU8" t="n">
-        <v>5.653927459547958e-08</v>
+        <v>0.0241775419563055</v>
       </c>
       <c r="CV8" t="n">
-        <v>8.237573290159617e-09</v>
+        <v>0.02216453850269318</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.305467067780341e-09</v>
+        <v>0.1377624124288559</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.65050861866689e-09</v>
+        <v>0.02775649726390839</v>
       </c>
       <c r="CY8" t="n">
-        <v>9.421861513203567e-09</v>
+        <v>0.1642730832099915</v>
       </c>
       <c r="CZ8" t="n">
-        <v>7.612699803871692e-09</v>
+        <v>0.01081487908959389</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.080437694866987e-08</v>
+        <v>0.05774903669953346</v>
       </c>
       <c r="DB8" t="n">
-        <v>5.362489119420388e-09</v>
+        <v>0.009669799357652664</v>
       </c>
       <c r="DC8" t="n">
-        <v>9.362566277815176e-10</v>
+        <v>0.04533882066607475</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.576810149117591e-08</v>
+        <v>0.003237962257117033</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.189178888694187e-08</v>
+        <v>0.05156189203262329</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.82684791130805e-08</v>
+        <v>0.1680982112884521</v>
       </c>
       <c r="DG8" t="n">
-        <v>6.157584664379101e-08</v>
+        <v>0.2364296764135361</v>
       </c>
       <c r="DH8" t="n">
-        <v>7.930472634143371e-08</v>
+        <v>0.08258600533008575</v>
       </c>
       <c r="DI8" t="n">
-        <v>9.131747447099769e-08</v>
+        <v>0.1066497191786766</v>
       </c>
       <c r="DJ8" t="n">
-        <v>4.628097372005868e-08</v>
+        <v>0.2063522040843964</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.503197980123332e-10</v>
+        <v>0.03030099906027317</v>
       </c>
       <c r="DL8" t="n">
-        <v>6.331335811182726e-08</v>
+        <v>0.1898311376571655</v>
       </c>
       <c r="DM8" t="n">
-        <v>2.936677212517225e-08</v>
+        <v>0.1069104969501495</v>
       </c>
       <c r="DN8" t="n">
-        <v>9.838122316807585e-09</v>
+        <v>0.03198991343379021</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.422657357532444e-08</v>
+        <v>0.06426830589771271</v>
       </c>
       <c r="DP8" t="n">
-        <v>1.306653985011508e-08</v>
+        <v>0.04954100400209427</v>
       </c>
       <c r="DQ8" t="n">
-        <v>8.798583195357423e-09</v>
+        <v>0.128587931394577</v>
       </c>
       <c r="DR8" t="n">
-        <v>2.237077190159198e-08</v>
+        <v>0.002246452029794455</v>
       </c>
       <c r="DS8" t="n">
-        <v>6.23634255347838e-09</v>
+        <v>0.0281580463051796</v>
       </c>
       <c r="DT8" t="n">
-        <v>6.195934432184913e-09</v>
+        <v>0.09590787440538406</v>
       </c>
       <c r="DU8" t="n">
-        <v>8.180930599621661e-09</v>
+        <v>0.02135757356882095</v>
       </c>
       <c r="DV8" t="n">
-        <v>2.949030530885466e-08</v>
+        <v>0.06300020962953568</v>
       </c>
       <c r="DW8" t="n">
-        <v>4.337135450782625e-08</v>
+        <v>0.01458371989428997</v>
       </c>
       <c r="DX8" t="n">
-        <v>6.941082375533369e-09</v>
+        <v>0.1263254731893539</v>
       </c>
       <c r="DY8" t="n">
-        <v>4.934179997917454e-08</v>
+        <v>0.0426507294178009</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.403238579835488e-08</v>
+        <v>0.1633471548557281</v>
       </c>
       <c r="EA8" t="n">
-        <v>2.058278703032101e-08</v>
+        <v>0.04943956062197685</v>
       </c>
       <c r="EB8" t="n">
-        <v>6.444149658335618e-10</v>
+        <v>0.007067493628710508</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.120718972127179e-08</v>
+        <v>0.04622077941894531</v>
       </c>
       <c r="ED8" t="n">
-        <v>1.63705706768269e-08</v>
+        <v>0.2183601707220078</v>
       </c>
       <c r="EE8" t="n">
-        <v>4.017147947621424e-09</v>
+        <v>0.1719339042901993</v>
       </c>
       <c r="EF8" t="n">
-        <v>7.67736274553954e-09</v>
+        <v>0.07775496691465378</v>
       </c>
       <c r="EG8" t="n">
-        <v>5.337091657509063e-09</v>
+        <v>0.1172941923141479</v>
       </c>
       <c r="EH8" t="n">
-        <v>2.329443304915912e-08</v>
+        <v>0.02502344734966755</v>
       </c>
       <c r="EI8" t="n">
-        <v>1.896744450391452e-08</v>
+        <v>0.08720214664936066</v>
       </c>
       <c r="EJ8" t="n">
-        <v>7.322544348653537e-09</v>
+        <v>0.1002320945262909</v>
       </c>
       <c r="EK8" t="n">
-        <v>1.538902516529106e-08</v>
+        <v>0.06939511746168137</v>
       </c>
       <c r="EL8" t="n">
-        <v>7.909089383417722e-09</v>
+        <v>0.02495574951171875</v>
       </c>
       <c r="EM8" t="n">
-        <v>2.735968340772388e-09</v>
+        <v>0.001702738460153341</v>
       </c>
       <c r="EN8" t="n">
-        <v>7.084230535525649e-09</v>
+        <v>0.02464719489216805</v>
       </c>
       <c r="EO8" t="n">
-        <v>7.646071331635085e-09</v>
+        <v>0.04480305314064026</v>
       </c>
       <c r="EP8" t="n">
-        <v>2.426577871972313e-08</v>
+        <v>0.00768013671040535</v>
       </c>
       <c r="EQ8" t="n">
-        <v>2.655194109024706e-08</v>
+        <v>0.02733980119228363</v>
       </c>
       <c r="ER8" t="n">
-        <v>2.136874455160864e-09</v>
+        <v>0.01193007826805115</v>
       </c>
       <c r="ES8" t="n">
-        <v>6.85062673255743e-09</v>
+        <v>0.02115310169756413</v>
       </c>
       <c r="ET8" t="n">
-        <v>9.067004924645516e-09</v>
+        <v>0.01812551915645599</v>
       </c>
       <c r="EU8" t="n">
-        <v>3.368292667005335e-08</v>
+        <v>0.07570888847112656</v>
       </c>
       <c r="EV8" t="n">
-        <v>5.403293457106884e-08</v>
+        <v>0.09552477300167084</v>
       </c>
       <c r="EW8" t="n">
-        <v>1.260787652057616e-08</v>
+        <v>0.06187582761049271</v>
       </c>
       <c r="EX8" t="n">
-        <v>1.229170543126656e-08</v>
+        <v>0.03161045163869858</v>
       </c>
       <c r="EY8" t="n">
-        <v>2.969860357637799e-09</v>
+        <v>0.156227633357048</v>
       </c>
       <c r="EZ8" t="n">
-        <v>1.003462313242665e-09</v>
+        <v>0.0191799309104681</v>
       </c>
       <c r="FA8" t="n">
-        <v>5.528095758933205e-10</v>
+        <v>0.1898303329944611</v>
       </c>
       <c r="FB8" t="n">
-        <v>1.122288750821099e-08</v>
+        <v>0.01125226728618145</v>
       </c>
       <c r="FC8" t="n">
-        <v>8.562152764568509e-09</v>
+        <v>0.03298276662826538</v>
       </c>
       <c r="FD8" t="n">
-        <v>4.361576433353775e-09</v>
+        <v>0.02024361304938793</v>
       </c>
       <c r="FE8" t="n">
-        <v>2.692549738725347e-09</v>
+        <v>0.07763508707284927</v>
       </c>
       <c r="FF8" t="n">
-        <v>1.370290370061866e-08</v>
+        <v>0.01611652225255966</v>
       </c>
       <c r="FG8" t="n">
-        <v>5.192580587731754e-09</v>
+        <v>0.1100510284304619</v>
       </c>
       <c r="FH8" t="n">
-        <v>9.017258051358112e-10</v>
+        <v>0.05484845116734505</v>
       </c>
       <c r="FI8" t="n">
-        <v>4.182489021786751e-08</v>
+        <v>0.01049208454787731</v>
       </c>
       <c r="FJ8" t="n">
-        <v>1.396772653095013e-08</v>
+        <v>0.1078350841999054</v>
       </c>
       <c r="FK8" t="n">
-        <v>3.564694095459231e-09</v>
+        <v>0.1302129775285721</v>
       </c>
       <c r="FL8" t="n">
-        <v>3.086367783566857e-08</v>
+        <v>0.01338781043887138</v>
       </c>
       <c r="FM8" t="n">
-        <v>1.475679023421606e-09</v>
+        <v>0.1284587979316711</v>
       </c>
       <c r="FN8" t="n">
-        <v>2.637059992594004e-08</v>
+        <v>0.09275809675455093</v>
       </c>
       <c r="FO8" t="n">
-        <v>2.282820510401962e-08</v>
+        <v>0.1025442332029343</v>
       </c>
       <c r="FP8" t="n">
-        <v>4.147378973584637e-08</v>
+        <v>0.1512857377529144</v>
       </c>
       <c r="FQ8" t="n">
-        <v>4.08214351210745e-10</v>
+        <v>0.2857513427734375</v>
       </c>
       <c r="FR8" t="n">
-        <v>4.581631074529469e-08</v>
+        <v>0.244355708360672</v>
       </c>
       <c r="FS8" t="n">
-        <v>4.990175384023132e-09</v>
+        <v>0.1904548853635788</v>
       </c>
       <c r="FT8" t="n">
-        <v>2.337160687204687e-09</v>
+        <v>0.1475488394498825</v>
       </c>
       <c r="FU8" t="n">
-        <v>3.552262484163293e-08</v>
+        <v>0.1167831569910049</v>
       </c>
       <c r="FV8" t="n">
-        <v>6.099097049627744e-08</v>
+        <v>0.03436765819787979</v>
       </c>
       <c r="FW8" t="n">
-        <v>6.149704301350312e-09</v>
+        <v>0.03237868845462799</v>
       </c>
       <c r="FX8" t="n">
-        <v>3.471654075326569e-09</v>
+        <v>0.1979048997163773</v>
       </c>
       <c r="FY8" t="n">
-        <v>1.149498718433506e-09</v>
+        <v>0.0931335836648941</v>
       </c>
       <c r="FZ8" t="n">
-        <v>3.301166273672607e-08</v>
+        <v>0.02002015151083469</v>
       </c>
       <c r="GA8" t="n">
-        <v>3.705616791194188e-08</v>
+        <v>0.01196934934705496</v>
       </c>
       <c r="GB8" t="n">
-        <v>6.957734832724327e-09</v>
+        <v>0.1110863834619522</v>
       </c>
       <c r="GC8" t="n">
-        <v>3.769984857626696e-08</v>
+        <v>0.05717504397034645</v>
       </c>
       <c r="GD8" t="n">
-        <v>1.79071228956218e-08</v>
+        <v>0.0321592316031456</v>
       </c>
       <c r="GE8" t="n">
-        <v>1.92876683513532e-08</v>
+        <v>0.1188041865825653</v>
       </c>
       <c r="GF8" t="n">
-        <v>2.324958003896427e-08</v>
+        <v>0.06980454921722412</v>
       </c>
       <c r="GG8" t="n">
-        <v>3.284970517825059e-08</v>
+        <v>0.08044449985027313</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9.175914250647565e-09</v>
+        <v>0.006694504525512457</v>
       </c>
       <c r="B9" t="n">
-        <v>2.136933296981169e-09</v>
+        <v>0.1469351351261139</v>
       </c>
       <c r="C9" t="n">
-        <v>1.115429260067913e-08</v>
+        <v>0.0002078283578157425</v>
       </c>
       <c r="D9" t="n">
-        <v>3.770529843905024e-08</v>
+        <v>0.06445974856615067</v>
       </c>
       <c r="E9" t="n">
-        <v>2.175427304962341e-08</v>
+        <v>0.04729044437408447</v>
       </c>
       <c r="F9" t="n">
-        <v>7.718470840245573e-08</v>
+        <v>0.1140934675931931</v>
       </c>
       <c r="G9" t="n">
-        <v>1.345774514049936e-08</v>
+        <v>0.02274435199797153</v>
       </c>
       <c r="H9" t="n">
-        <v>2.01149674694534e-08</v>
+        <v>0.07968702912330627</v>
       </c>
       <c r="I9" t="n">
-        <v>3.117479829839453e-09</v>
+        <v>0.03231676667928696</v>
       </c>
       <c r="J9" t="n">
-        <v>2.971578094701499e-09</v>
+        <v>0.02358120121061802</v>
       </c>
       <c r="K9" t="n">
-        <v>8.126846751110861e-09</v>
+        <v>0.1445818990468979</v>
       </c>
       <c r="L9" t="n">
-        <v>2.158229150950319e-08</v>
+        <v>0.03841568529605865</v>
       </c>
       <c r="M9" t="n">
-        <v>2.030543200248758e-08</v>
+        <v>0.09035376459360123</v>
       </c>
       <c r="N9" t="n">
-        <v>1.615804734456106e-08</v>
+        <v>0.05942635238170624</v>
       </c>
       <c r="O9" t="n">
-        <v>5.558953120043952e-08</v>
+        <v>0.1529686152935028</v>
       </c>
       <c r="P9" t="n">
-        <v>1.412410366441463e-08</v>
+        <v>0.01514261867851019</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.19425970726661e-08</v>
+        <v>0.108864814043045</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23378649519168e-08</v>
+        <v>0.05676648393273354</v>
       </c>
       <c r="S9" t="n">
-        <v>9.79039072035448e-09</v>
+        <v>0.02682962268590927</v>
       </c>
       <c r="T9" t="n">
-        <v>1.556974282834744e-08</v>
+        <v>0.04335616901516914</v>
       </c>
       <c r="U9" t="n">
-        <v>7.538281110441858e-09</v>
+        <v>0.01661805063486099</v>
       </c>
       <c r="V9" t="n">
-        <v>1.322039588913526e-09</v>
+        <v>0.0004954622127115726</v>
       </c>
       <c r="W9" t="n">
-        <v>6.010420161572938e-09</v>
+        <v>0.003205172251909971</v>
       </c>
       <c r="X9" t="n">
-        <v>5.747502029862517e-09</v>
+        <v>0.007765751797705889</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.746566695246202e-09</v>
+        <v>0.00452614389359951</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.259129380405739e-09</v>
+        <v>0.01387844793498516</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.924585349565859e-09</v>
+        <v>0.01100828871130943</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.170442183403793e-11</v>
+        <v>0.01125930342823267</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.019526152390426e-08</v>
+        <v>0.05528158321976662</v>
       </c>
       <c r="AD9" t="n">
-        <v>9.090019403856786e-09</v>
+        <v>0.002652873983606696</v>
       </c>
       <c r="AE9" t="n">
-        <v>8.251989314089769e-09</v>
+        <v>0.0009000515565276146</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.928990074570265e-09</v>
+        <v>0.02030260674655437</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.187340359365407e-08</v>
+        <v>0.004804494325071573</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.224361168006283e-09</v>
+        <v>0.02332549914717674</v>
       </c>
       <c r="AI9" t="n">
-        <v>8.279804397659518e-09</v>
+        <v>0.001709222793579102</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4.679142850960716e-09</v>
+        <v>0.03116602636873722</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.081087308563156e-08</v>
+        <v>0.03385567665100098</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.855750042523141e-08</v>
+        <v>0.04163959622383118</v>
       </c>
       <c r="AM9" t="n">
-        <v>5.900119948165639e-09</v>
+        <v>0.02302808314561844</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.24422139258229e-09</v>
+        <v>0.0177076980471611</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.159149931595493e-08</v>
+        <v>0.005393450148403645</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.981031504451948e-09</v>
+        <v>0.02339103631675243</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.411600474871989e-09</v>
+        <v>0.003605685196816921</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.021976250991656e-10</v>
+        <v>0.01514176744967699</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.707219916776921e-09</v>
+        <v>0.006869229953736067</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.15661307992832e-09</v>
+        <v>0.006163343787193298</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.032523008376756e-09</v>
+        <v>0.01157048717141151</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.781121638013474e-09</v>
+        <v>0.000836862251162529</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.231359002597856e-08</v>
+        <v>0.01372511405497789</v>
       </c>
       <c r="AX9" t="n">
-        <v>2.150830802349901e-08</v>
+        <v>0.05725211650133133</v>
       </c>
       <c r="AY9" t="n">
-        <v>2.13885709143824e-08</v>
+        <v>0.06496374309062958</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.735701275571103e-10</v>
+        <v>0.03983810544013977</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.636432100937668e-09</v>
+        <v>0.03551515564322472</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.697240653048993e-09</v>
+        <v>0.02993898838758469</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.397929462944376e-09</v>
+        <v>0.01779936626553535</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.010997921634953e-09</v>
+        <v>0.04297564178705215</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.342526338518837e-10</v>
+        <v>0.02314384654164314</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.449923262152879e-09</v>
+        <v>0.01774996891617775</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.420569048122161e-09</v>
+        <v>0.03785573691129684</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.212223020909732e-08</v>
+        <v>0.005544022191315889</v>
       </c>
       <c r="BI9" t="n">
-        <v>5.911798162117066e-09</v>
+        <v>0.02396666631102562</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1.483251832468113e-08</v>
+        <v>0.04290842637419701</v>
       </c>
       <c r="BK9" t="n">
-        <v>8.565103293278753e-09</v>
+        <v>0.005382970906794071</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.107100633390701e-08</v>
+        <v>0.01349258702248335</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.717155034304142e-08</v>
+        <v>0.07281724363565445</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.236638613733021e-08</v>
+        <v>0.02698825113475323</v>
       </c>
       <c r="BO9" t="n">
-        <v>6.200013835666596e-09</v>
+        <v>0.02743135206401348</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.327022296024552e-09</v>
+        <v>0.03876506164669991</v>
       </c>
       <c r="BQ9" t="n">
-        <v>9.421824431754544e-11</v>
+        <v>0.0220787413418293</v>
       </c>
       <c r="BR9" t="n">
-        <v>4.41458070099543e-09</v>
+        <v>0.02521909587085247</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.521636233154823e-10</v>
+        <v>0.007011804264038801</v>
       </c>
       <c r="BT9" t="n">
-        <v>4.766367744934996e-09</v>
+        <v>0.01196342706680298</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.388682235869965e-08</v>
+        <v>0.02442768216133118</v>
       </c>
       <c r="BV9" t="n">
-        <v>3.582838248306075e-09</v>
+        <v>0.05584979802370071</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.190827602139734e-09</v>
+        <v>0.0132930763065815</v>
       </c>
       <c r="BX9" t="n">
-        <v>1.200462929062951e-08</v>
+        <v>0.0349041186273098</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.674124921497878e-09</v>
+        <v>0.02501538209617138</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1.672982818945457e-08</v>
+        <v>0.0445818305015564</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.756438188811217e-09</v>
+        <v>0.01271035615354776</v>
       </c>
       <c r="CB9" t="n">
-        <v>2.643119278999961e-09</v>
+        <v>0.01211920659989119</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.820651433590228e-09</v>
+        <v>0.005583341233432293</v>
       </c>
       <c r="CD9" t="n">
-        <v>2.789548592119218e-10</v>
+        <v>0.01126929651945829</v>
       </c>
       <c r="CE9" t="n">
-        <v>8.280624519407809e-10</v>
+        <v>0.02737468667328358</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.263377929523358e-09</v>
+        <v>0.004545513540506363</v>
       </c>
       <c r="CG9" t="n">
-        <v>7.4186456977543e-09</v>
+        <v>0.02243371680378914</v>
       </c>
       <c r="CH9" t="n">
-        <v>4.50091652837159e-09</v>
+        <v>0.02133995853364468</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.533597604463921e-08</v>
+        <v>0.02073291316628456</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.165505192357585e-10</v>
+        <v>0.004576203413307667</v>
       </c>
       <c r="CK9" t="n">
-        <v>4.395174002524982e-09</v>
+        <v>0.002993111498653889</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.806735649978464e-09</v>
+        <v>0.007185453083366156</v>
       </c>
       <c r="CM9" t="n">
-        <v>8.342396995431045e-09</v>
+        <v>0.07050422579050064</v>
       </c>
       <c r="CN9" t="n">
-        <v>3.477054866252161e-09</v>
+        <v>0.0223403200507164</v>
       </c>
       <c r="CO9" t="n">
-        <v>3.870833431562914e-09</v>
+        <v>0.02222842909395695</v>
       </c>
       <c r="CP9" t="n">
-        <v>3.60518659370257e-09</v>
+        <v>0.03098693862557411</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.432198886737069e-09</v>
+        <v>0.03211192786693573</v>
       </c>
       <c r="CR9" t="n">
-        <v>9.317325799784726e-10</v>
+        <v>0.009982091374695301</v>
       </c>
       <c r="CS9" t="n">
-        <v>1.016049999691404e-08</v>
+        <v>0.009217552840709686</v>
       </c>
       <c r="CT9" t="n">
-        <v>9.234150333270463e-09</v>
+        <v>0.02427821233868599</v>
       </c>
       <c r="CU9" t="n">
-        <v>8.326738409891732e-09</v>
+        <v>0.00405805604532361</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.003196053479428e-09</v>
+        <v>0.008711198344826698</v>
       </c>
       <c r="CW9" t="n">
-        <v>4.09674516532732e-10</v>
+        <v>0.02662578970193863</v>
       </c>
       <c r="CX9" t="n">
-        <v>5.37050937055028e-09</v>
+        <v>0.01204024255275726</v>
       </c>
       <c r="CY9" t="n">
-        <v>8.736982692880702e-09</v>
+        <v>0.01546873338520527</v>
       </c>
       <c r="CZ9" t="n">
-        <v>7.317179750998548e-09</v>
+        <v>0.01892294175922871</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.168343377599967e-08</v>
+        <v>0.02898889221251011</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.431900154003074e-09</v>
+        <v>0.00738857313990593</v>
       </c>
       <c r="DC9" t="n">
-        <v>5.982855100228335e-09</v>
+        <v>0.00553761376067996</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.950365285414591e-09</v>
+        <v>0.009603816084563732</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.570601426692519e-08</v>
+        <v>0.01173168513923883</v>
       </c>
       <c r="DF9" t="n">
-        <v>3.886505783867733e-09</v>
+        <v>0.03714349865913391</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.661455766883591e-08</v>
+        <v>0.007728012278676033</v>
       </c>
       <c r="DH9" t="n">
-        <v>1.627966206285691e-09</v>
+        <v>0.01968885771930218</v>
       </c>
       <c r="DI9" t="n">
-        <v>5.072892328428225e-09</v>
+        <v>0.07092166692018509</v>
       </c>
       <c r="DJ9" t="n">
-        <v>6.000557828400588e-10</v>
+        <v>0.03011574596166611</v>
       </c>
       <c r="DK9" t="n">
-        <v>1.366807378389012e-08</v>
+        <v>0.02189580164849758</v>
       </c>
       <c r="DL9" t="n">
-        <v>7.403881063794415e-09</v>
+        <v>0.004324836656451225</v>
       </c>
       <c r="DM9" t="n">
-        <v>1.076739941652249e-08</v>
+        <v>0.01011539716273546</v>
       </c>
       <c r="DN9" t="n">
-        <v>9.641240694691078e-09</v>
+        <v>0.0009731268510222435</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.02864569587291e-08</v>
+        <v>0.03606833517551422</v>
       </c>
       <c r="DP9" t="n">
-        <v>2.914070318382755e-09</v>
+        <v>0.006947255227714777</v>
       </c>
       <c r="DQ9" t="n">
-        <v>1.218398382185626e-09</v>
+        <v>0.003396934596821666</v>
       </c>
       <c r="DR9" t="n">
-        <v>1.482635614280525e-08</v>
+        <v>0.00635463884100318</v>
       </c>
       <c r="DS9" t="n">
-        <v>1.190951159912856e-08</v>
+        <v>8.40140855871141e-05</v>
       </c>
       <c r="DT9" t="n">
-        <v>2.172288793289567e-09</v>
+        <v>0.008328787982463837</v>
       </c>
       <c r="DU9" t="n">
-        <v>4.131320618938616e-09</v>
+        <v>0.0007610338507220149</v>
       </c>
       <c r="DV9" t="n">
-        <v>9.694414160321685e-09</v>
+        <v>0.04087459295988083</v>
       </c>
       <c r="DW9" t="n">
-        <v>1.086463363719758e-08</v>
+        <v>0.02901971153914928</v>
       </c>
       <c r="DX9" t="n">
-        <v>1.698293417007335e-08</v>
+        <v>0.02175082266330719</v>
       </c>
       <c r="DY9" t="n">
-        <v>2.10477875128845e-08</v>
+        <v>0.01957054063677788</v>
       </c>
       <c r="DZ9" t="n">
-        <v>1.079239986268021e-08</v>
+        <v>0.00926101952791214</v>
       </c>
       <c r="EA9" t="n">
-        <v>5.060561303338318e-09</v>
+        <v>0.0213890727609396</v>
       </c>
       <c r="EB9" t="n">
-        <v>7.946391988866708e-09</v>
+        <v>0.01467603351920843</v>
       </c>
       <c r="EC9" t="n">
-        <v>9.56215462366572e-09</v>
+        <v>0.01158562116324902</v>
       </c>
       <c r="ED9" t="n">
-        <v>2.30258612177181e-09</v>
+        <v>0.02820303477346897</v>
       </c>
       <c r="EE9" t="n">
-        <v>4.442638701362966e-09</v>
+        <v>0.002156414091587067</v>
       </c>
       <c r="EF9" t="n">
-        <v>4.790501328955088e-09</v>
+        <v>0.008123079314827919</v>
       </c>
       <c r="EG9" t="n">
-        <v>4.1586187826681e-09</v>
+        <v>0.04761961847543716</v>
       </c>
       <c r="EH9" t="n">
-        <v>2.48078646514216e-09</v>
+        <v>0.01849161460995674</v>
       </c>
       <c r="EI9" t="n">
-        <v>1.661037529743226e-08</v>
+        <v>0.03296299278736115</v>
       </c>
       <c r="EJ9" t="n">
-        <v>7.751093100694106e-09</v>
+        <v>0.03613043203949928</v>
       </c>
       <c r="EK9" t="n">
-        <v>7.723575556894957e-09</v>
+        <v>0.01682012341916561</v>
       </c>
       <c r="EL9" t="n">
-        <v>4.26491231220183e-10</v>
+        <v>0.01424577552825212</v>
       </c>
       <c r="EM9" t="n">
-        <v>9.433279712922626e-10</v>
+        <v>0.01461719069629908</v>
       </c>
       <c r="EN9" t="n">
-        <v>4.545143816869768e-09</v>
+        <v>0.01177870854735374</v>
       </c>
       <c r="EO9" t="n">
-        <v>8.536858331353869e-09</v>
+        <v>0.0005546521861106157</v>
       </c>
       <c r="EP9" t="n">
-        <v>6.694817145103116e-09</v>
+        <v>0.004177134484052658</v>
       </c>
       <c r="EQ9" t="n">
-        <v>1.512537650683043e-08</v>
+        <v>0.002997889183461666</v>
       </c>
       <c r="ER9" t="n">
-        <v>9.275285428600455e-09</v>
+        <v>0.000113088171929121</v>
       </c>
       <c r="ES9" t="n">
-        <v>1.039435915117792e-08</v>
+        <v>0.03548722714185715</v>
       </c>
       <c r="ET9" t="n">
-        <v>2.459633829943186e-09</v>
+        <v>0.01896617561578751</v>
       </c>
       <c r="EU9" t="n">
-        <v>2.065476678581035e-09</v>
+        <v>0.01365160476416349</v>
       </c>
       <c r="EV9" t="n">
-        <v>1.20780043744162e-08</v>
+        <v>0.001453983597457409</v>
       </c>
       <c r="EW9" t="n">
-        <v>1.224520129738949e-08</v>
+        <v>0.01729987002909184</v>
       </c>
       <c r="EX9" t="n">
-        <v>2.610355043231039e-09</v>
+        <v>0.01266838982701302</v>
       </c>
       <c r="EY9" t="n">
-        <v>1.110311287355614e-09</v>
+        <v>0.03021397069096565</v>
       </c>
       <c r="EZ9" t="n">
-        <v>6.041383393551314e-09</v>
+        <v>0.001853043911978602</v>
       </c>
       <c r="FA9" t="n">
-        <v>9.796175426401987e-09</v>
+        <v>0.02256117016077042</v>
       </c>
       <c r="FB9" t="n">
-        <v>3.648993551763624e-09</v>
+        <v>0.02142542600631714</v>
       </c>
       <c r="FC9" t="n">
-        <v>1.183040509999955e-08</v>
+        <v>0.02749538607895374</v>
       </c>
       <c r="FD9" t="n">
-        <v>2.314138325409942e-10</v>
+        <v>0.00775864627212286</v>
       </c>
       <c r="FE9" t="n">
-        <v>5.988025186809409e-09</v>
+        <v>0.01066930312663317</v>
       </c>
       <c r="FF9" t="n">
-        <v>1.12602949187135e-09</v>
+        <v>0.001006658538244665</v>
       </c>
       <c r="FG9" t="n">
-        <v>1.555571671474354e-09</v>
+        <v>0.006719666998833418</v>
       </c>
       <c r="FH9" t="n">
-        <v>6.78762734906968e-09</v>
+        <v>0.02043523080646992</v>
       </c>
       <c r="FI9" t="n">
-        <v>2.038322399755543e-08</v>
+        <v>0.01583066210150719</v>
       </c>
       <c r="FJ9" t="n">
-        <v>9.114303978208227e-09</v>
+        <v>0.01495735254138708</v>
       </c>
       <c r="FK9" t="n">
-        <v>1.774400004705967e-08</v>
+        <v>0.01899641938507557</v>
       </c>
       <c r="FL9" t="n">
-        <v>5.851129802891819e-09</v>
+        <v>0.004033295903354883</v>
       </c>
       <c r="FM9" t="n">
-        <v>9.971445891210351e-09</v>
+        <v>0.006919455248862505</v>
       </c>
       <c r="FN9" t="n">
-        <v>1.69308589370587e-09</v>
+        <v>0.04136964306235313</v>
       </c>
       <c r="FO9" t="n">
-        <v>7.57452855992824e-09</v>
+        <v>0.06653376668691635</v>
       </c>
       <c r="FP9" t="n">
-        <v>9.672723066955768e-09</v>
+        <v>0.09095165878534317</v>
       </c>
       <c r="FQ9" t="n">
-        <v>4.86199480675964e-09</v>
+        <v>0.06415218114852905</v>
       </c>
       <c r="FR9" t="n">
-        <v>1.425608076033313e-09</v>
+        <v>0.01478185132145882</v>
       </c>
       <c r="FS9" t="n">
-        <v>2.191893777592213e-09</v>
+        <v>0.02936272136867046</v>
       </c>
       <c r="FT9" t="n">
-        <v>2.967628809358303e-08</v>
+        <v>0.030305165797472</v>
       </c>
       <c r="FU9" t="n">
-        <v>6.577701050503038e-09</v>
+        <v>0.003320991527289152</v>
       </c>
       <c r="FV9" t="n">
-        <v>4.071577741626697e-09</v>
+        <v>0.06220950931310654</v>
       </c>
       <c r="FW9" t="n">
-        <v>6.061129376178087e-11</v>
+        <v>0.06270533055067062</v>
       </c>
       <c r="FX9" t="n">
-        <v>5.949995607323899e-09</v>
+        <v>0.01903189159929752</v>
       </c>
       <c r="FY9" t="n">
-        <v>1.071545407960173e-09</v>
+        <v>0.008384495042264462</v>
       </c>
       <c r="FZ9" t="n">
-        <v>2.064243176391756e-08</v>
+        <v>0.02909635752439499</v>
       </c>
       <c r="GA9" t="n">
-        <v>6.882432401766891e-09</v>
+        <v>0.03121668100357056</v>
       </c>
       <c r="GB9" t="n">
-        <v>8.670690831991124e-09</v>
+        <v>0.02644228562712669</v>
       </c>
       <c r="GC9" t="n">
-        <v>2.546890343069208e-08</v>
+        <v>0.05201490968465805</v>
       </c>
       <c r="GD9" t="n">
-        <v>1.13515650213003e-08</v>
+        <v>0.007808825001120567</v>
       </c>
       <c r="GE9" t="n">
-        <v>7.01180891127251e-09</v>
+        <v>0.02399978414177895</v>
       </c>
       <c r="GF9" t="n">
-        <v>1.925337000940885e-09</v>
+        <v>0.02338984049856663</v>
       </c>
       <c r="GG9" t="n">
-        <v>1.294419349484599e-09</v>
+        <v>0.007318081799894571</v>
       </c>
     </row>
     <row r="10">
@@ -7258,1709 +7258,1709 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.02620433084666729</v>
+        <v>0.1487489491701126</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1625630408525467</v>
+        <v>0.5587641596794128</v>
       </c>
       <c r="C13" t="n">
-        <v>0.007369479164481163</v>
+        <v>0.1943879276514053</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1036650612950325</v>
+        <v>0.03118784725666046</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008833626285195351</v>
+        <v>0.02707447856664658</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1547589004039764</v>
+        <v>0.2186526209115982</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02962768822908401</v>
+        <v>0.009592205286026001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0532512441277504</v>
+        <v>0.01738429442048073</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02423838898539543</v>
+        <v>0.1366115212440491</v>
       </c>
       <c r="J13" t="n">
-        <v>0.04607455804944038</v>
+        <v>0.04559594392776489</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1366400867700577</v>
+        <v>0.9112516045570374</v>
       </c>
       <c r="L13" t="n">
-        <v>0.008767541497945786</v>
+        <v>0.2480238080024719</v>
       </c>
       <c r="M13" t="n">
-        <v>0.09355147927999496</v>
+        <v>0.1941857933998108</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02044802717864513</v>
+        <v>0.1933421492576599</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1547531485557556</v>
+        <v>0.3226320147514343</v>
       </c>
       <c r="P13" t="n">
-        <v>0.02900668047368526</v>
+        <v>0.2071282565593719</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.008361493237316608</v>
+        <v>0.3113859891891479</v>
       </c>
       <c r="R13" t="n">
-        <v>0.02375517413020134</v>
+        <v>0.1550207585096359</v>
       </c>
       <c r="S13" t="n">
-        <v>0.00163926079403609</v>
+        <v>0.1572199165821075</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01491771545261145</v>
+        <v>0.2405309826135635</v>
       </c>
       <c r="U13" t="n">
-        <v>0.009577157907187939</v>
+        <v>0.05602310597896576</v>
       </c>
       <c r="V13" t="n">
-        <v>0.03463337197899818</v>
+        <v>0.2724701464176178</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02896359376609325</v>
+        <v>0.2321222722530365</v>
       </c>
       <c r="X13" t="n">
-        <v>0.009227629750967026</v>
+        <v>0.03888384252786636</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.01498647406697273</v>
+        <v>0.09052444994449615</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.02756420336663723</v>
+        <v>0.2305095642805099</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.02168102748692036</v>
+        <v>0.0456392765045166</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.008543414995074272</v>
+        <v>0.1729840487241745</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.009641565382480621</v>
+        <v>0.0862051248550415</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.009476873092353344</v>
+        <v>0.01509915199130774</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.004494990222156048</v>
+        <v>0.1628293544054031</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.007588244043290615</v>
+        <v>0.5129461288452148</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.01835079118609428</v>
+        <v>0.2740201354026794</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.01115202251821756</v>
+        <v>0.08190114051103592</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.007347557228058577</v>
+        <v>0.1041086837649345</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.01587040908634663</v>
+        <v>0.07959569990634918</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0295365396887064</v>
+        <v>0.04799661785364151</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01993954181671143</v>
+        <v>0.187919020652771</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.002600298263132572</v>
+        <v>0.01076623424887657</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.005828710272908211</v>
+        <v>0.1661686897277832</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.003538534278050065</v>
+        <v>0.03974473103880882</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.02718522027134895</v>
+        <v>0.04839630052447319</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.00606278283521533</v>
+        <v>0.1553100049495697</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.01533396821469069</v>
+        <v>0.276698499917984</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.01923454366624355</v>
+        <v>0.07714866101741791</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.01281832344830036</v>
+        <v>0.09266660362482071</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.1166501194238663</v>
+        <v>0.9744449853897095</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.004844744689762592</v>
+        <v>0.1195046454668045</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.01697763800621033</v>
+        <v>0.04208792001008987</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.005966796539723873</v>
+        <v>0.1046571135520935</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.08068947494029999</v>
+        <v>0.3807337880134583</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.007660307921469212</v>
+        <v>0.006735524162650108</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0229332447052002</v>
+        <v>0.06637995690107346</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.04030207544565201</v>
+        <v>0.1166214942932129</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.02706237323582172</v>
+        <v>0.05518563091754913</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.04523194581270218</v>
+        <v>0.1455427706241608</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.04671084508299828</v>
+        <v>0.1109217777848244</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.02459359169006348</v>
+        <v>0.02750670164823532</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.02345607057213783</v>
+        <v>0.2971364855766296</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.05469697713851929</v>
+        <v>0.03987082466483116</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.005182401742786169</v>
+        <v>0.1847235560417175</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.02455797791481018</v>
+        <v>0.02633409202098846</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.006882552988827229</v>
+        <v>0.06006253883242607</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.006606573704630136</v>
+        <v>0.1495187729597092</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.05544756725430489</v>
+        <v>0.0990765392780304</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.009289640001952648</v>
+        <v>0.01200393028557301</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.02143483236432076</v>
+        <v>0.1367583423852921</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.02123954519629478</v>
+        <v>0.07222191989421844</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.005237782839685678</v>
+        <v>0.1179295033216476</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.02044288069009781</v>
+        <v>0.08425995707511902</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.01325099170207977</v>
+        <v>0.05394186824560165</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0001926752738654613</v>
+        <v>0.05118761211633682</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.006009210366755724</v>
+        <v>0.2049607783555984</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.06299879401922226</v>
+        <v>0.6286604404449463</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.01486259885132313</v>
+        <v>0.02484659105539322</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.02718273364007473</v>
+        <v>0.3105990886688232</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.003062496427446604</v>
+        <v>0.1279072910547256</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0365273617208004</v>
+        <v>0.1810374706983566</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.009921745397150517</v>
+        <v>0.05168889462947845</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.005223043262958527</v>
+        <v>0.1436374336481094</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.02541003562510014</v>
+        <v>0.05172249302268028</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.001915775123052299</v>
+        <v>0.06092880666255951</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.02086746506392956</v>
+        <v>0.1901889741420746</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.02048926800489426</v>
+        <v>0.02138692513108253</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0185958705842495</v>
+        <v>0.04012051224708557</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.01041124761104584</v>
+        <v>0.05690474808216095</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.02060766145586967</v>
+        <v>0.1022080928087234</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.01282194256782532</v>
+        <v>0.1029634177684784</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0125113083049655</v>
+        <v>0.0300239622592926</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.01246373914182186</v>
+        <v>0.04451680928468704</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.02959324233233929</v>
+        <v>0.1380067467689514</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.02656352892518044</v>
+        <v>0.6248594522476196</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.005361232440918684</v>
+        <v>0.05963125452399254</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.01780389994382858</v>
+        <v>0.2645373344421387</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.003408873453736305</v>
+        <v>0.3855265974998474</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0004484066739678383</v>
+        <v>0.2537412345409393</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0146835669875145</v>
+        <v>0.09278576821088791</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.01843849383294582</v>
+        <v>0.04657154530286789</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.003210222814232111</v>
+        <v>0.1849662214517593</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0006099896272644401</v>
+        <v>0.02974545955657959</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.017901960760355</v>
+        <v>0.1750135123729706</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.01836326532065868</v>
+        <v>0.02991762012243271</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.02619011327624321</v>
+        <v>0.04134932905435562</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.009293004870414734</v>
+        <v>0.01782545819878578</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.02166216820478439</v>
+        <v>0.1002263575792313</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.01498304214328527</v>
+        <v>0.05839711427688599</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.02289460599422455</v>
+        <v>0.006038757041096687</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.004938103258609772</v>
+        <v>0.06857755780220032</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.001138526480644941</v>
+        <v>0.1215205788612366</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.01522280462086201</v>
+        <v>0.08945892751216888</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.008833379484713078</v>
+        <v>0.02945325151085854</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.1036456003785133</v>
+        <v>0.1282565742731094</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0112052820622921</v>
+        <v>0.2879583537578583</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.008087888360023499</v>
+        <v>0.09416911005973816</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.01191198453307152</v>
+        <v>0.1726158559322357</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.02825925126671791</v>
+        <v>0.1005919799208641</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.02165839448571205</v>
+        <v>0.01188173145055771</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.01022202242165804</v>
+        <v>0.07926556468009949</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.008316334336996078</v>
+        <v>0.153019517660141</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.01748614758253098</v>
+        <v>0.002221133559942245</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.003844284452497959</v>
+        <v>0.1839397698640823</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.003949547652155161</v>
+        <v>0.1426757425069809</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.001878701848909259</v>
+        <v>0.01684596203267574</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.01811949163675308</v>
+        <v>0.1188052594661713</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.000539424829185009</v>
+        <v>0.2577335238456726</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.02121624350547791</v>
+        <v>0.02129921689629555</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0015070466324687</v>
+        <v>0.1609572619199753</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.001945187454111874</v>
+        <v>0.03321687132120132</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.01714527048170567</v>
+        <v>0.08000081777572632</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.01122249849140644</v>
+        <v>0.003106851130723953</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.005997250322252512</v>
+        <v>0.1640048921108246</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.01347461622208357</v>
+        <v>0.2050632238388062</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.007489819079637527</v>
+        <v>0.08723254501819611</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.00228352565318346</v>
+        <v>0.02924228832125664</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.004034289158880711</v>
+        <v>0.01702394708991051</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.009706985205411911</v>
+        <v>0.03639493137598038</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.01220774184912443</v>
+        <v>0.02283201925456524</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.01462601218372583</v>
+        <v>0.02021332085132599</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.01018572133034468</v>
+        <v>0.1223573833703995</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0004217363893985748</v>
+        <v>0.07714848220348358</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.02442609705030918</v>
+        <v>0.01693066582083702</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.008634529076516628</v>
+        <v>0.09594554454088211</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.003221737453714013</v>
+        <v>0.09610641747713089</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.003955864813178778</v>
+        <v>0.03679804876446724</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.007922972552478313</v>
+        <v>0.01844510436058044</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.004777438007295132</v>
+        <v>0.0416826568543911</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.01626287028193474</v>
+        <v>0.0303486417979002</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.01895583607256413</v>
+        <v>0.1116146966814995</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.001181291649118066</v>
+        <v>0.05967885628342628</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.00683626951649785</v>
+        <v>0.006280831061303616</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0226419921964407</v>
+        <v>0.07389730960130692</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.05918643996119499</v>
+        <v>0.104189395904541</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.01111357472836971</v>
+        <v>0.07093915343284607</v>
       </c>
       <c r="EX13" t="n">
-        <v>6.221083458513021e-05</v>
+        <v>0.07082794606685638</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.01559021882712841</v>
+        <v>0.1987692713737488</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.01520712859928608</v>
+        <v>0.01955764554440975</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.0204820167273283</v>
+        <v>0.03795778751373291</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.005692728329449892</v>
+        <v>0.01420368812978268</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0178968571126461</v>
+        <v>0.1134137138724327</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.021457364782691</v>
+        <v>0.1445287764072418</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.01495361141860485</v>
+        <v>0.02073418907821178</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.01205797307193279</v>
+        <v>0.05960773676633835</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.006032861769199371</v>
+        <v>0.1058711633086205</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.01563992910087109</v>
+        <v>0.2249119877815247</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.01319282501935959</v>
+        <v>0.05992552638053894</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.01930096000432968</v>
+        <v>0.2128706574440002</v>
       </c>
       <c r="FK13" t="n">
-        <v>6.790034240111709e-05</v>
+        <v>0.199320062994957</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.02321168035268784</v>
+        <v>0.02890277467668056</v>
       </c>
       <c r="FM13" t="n">
-        <v>9.811297059059143e-05</v>
+        <v>0.2041301131248474</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.01990045979619026</v>
+        <v>0.2204051464796066</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.007701684255152941</v>
+        <v>0.1725239753723145</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0135606937110424</v>
+        <v>0.008711569011211395</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.005173347890377045</v>
+        <v>0.2780651152133942</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.01955744996666908</v>
+        <v>0.08064235746860504</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.03521304205060005</v>
+        <v>0.2249191999435425</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.001622440759092569</v>
+        <v>0.002504767850041389</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.01636040024459362</v>
+        <v>0.007184375077486038</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.01889514923095703</v>
+        <v>0.1845589578151703</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.001115520019084215</v>
+        <v>0.01819095760583878</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.00712584936991334</v>
+        <v>0.157189279794693</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.03277172148227692</v>
+        <v>0.1401199400424957</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.00221226061694324</v>
+        <v>0.07162056863307953</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.006149365566670895</v>
+        <v>0.01245357654988766</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.005887632723897696</v>
+        <v>0.1287062615156174</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.01041922625154257</v>
+        <v>0.07738000154495239</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.02629020251333714</v>
+        <v>0.04567780718207359</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.07808005064725876</v>
+        <v>0.1188828945159912</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.004865140188485384</v>
+        <v>0.1429913341999054</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.01678404957056046</v>
+        <v>0.2106338888406754</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.0004390071844682097</v>
+        <v>0.02114612609148026</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1668816059827805</v>
+        <v>0.5726921558380127</v>
       </c>
       <c r="C14" t="n">
-        <v>0.02141944319009781</v>
+        <v>0.001097425818443298</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1192015931010246</v>
+        <v>0.4184753000736237</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07956826686859131</v>
+        <v>0.2269171178340912</v>
       </c>
       <c r="F14" t="n">
-        <v>0.07096609473228455</v>
+        <v>0.02279546484351158</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01381024345755577</v>
+        <v>0.01367473229765892</v>
       </c>
       <c r="H14" t="n">
-        <v>0.04139907285571098</v>
+        <v>0.2019202262163162</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01509724371135235</v>
+        <v>0.06689797341823578</v>
       </c>
       <c r="J14" t="n">
-        <v>0.005401910282671452</v>
+        <v>0.04163185879588127</v>
       </c>
       <c r="K14" t="n">
-        <v>0.134874701499939</v>
+        <v>0.5735790729522705</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01403117459267378</v>
+        <v>0.01729553937911987</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1147332787513733</v>
+        <v>0.528247594833374</v>
       </c>
       <c r="N14" t="n">
-        <v>0.09553638100624084</v>
+        <v>0.4998641610145569</v>
       </c>
       <c r="O14" t="n">
-        <v>0.07981357723474503</v>
+        <v>0.03388208523392677</v>
       </c>
       <c r="P14" t="n">
-        <v>0.01882201060652733</v>
+        <v>0.06301875412464142</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01125381886959076</v>
+        <v>0.07835490256547928</v>
       </c>
       <c r="R14" t="n">
-        <v>0.03210334852337837</v>
+        <v>0.09059035778045654</v>
       </c>
       <c r="S14" t="n">
-        <v>0.004852649755775928</v>
+        <v>0.002767532598227262</v>
       </c>
       <c r="T14" t="n">
-        <v>0.02168729528784752</v>
+        <v>0.02463990449905396</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01802690699696541</v>
+        <v>0.004856160841882229</v>
       </c>
       <c r="V14" t="n">
-        <v>0.03795328363776207</v>
+        <v>0.07853109389543533</v>
       </c>
       <c r="W14" t="n">
-        <v>0.04291402921080589</v>
+        <v>0.002917000092566013</v>
       </c>
       <c r="X14" t="n">
-        <v>0.02019067294895649</v>
+        <v>0.06303561478853226</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0009157417807728052</v>
+        <v>0.01697833091020584</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.01297765038907528</v>
+        <v>0.0597633421421051</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01298646070063114</v>
+        <v>0.07490025460720062</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.001959564164280891</v>
+        <v>0.02246903069317341</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.01908646337687969</v>
+        <v>0.02969259023666382</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.005438222549855709</v>
+        <v>0.07461709529161453</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.01077514234930277</v>
+        <v>0.2006286829710007</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.03721179068088531</v>
+        <v>0.2039584517478943</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.01990124955773354</v>
+        <v>0.2065580189228058</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.008414683863520622</v>
+        <v>0.05771640688180923</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.01160756312310696</v>
+        <v>0.1894417107105255</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.02004199288785458</v>
+        <v>0.01045447401702404</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.001219010562635958</v>
+        <v>0.01730711385607719</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.02130866795778275</v>
+        <v>0.1460694968700409</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.001260299701243639</v>
+        <v>0.06616093963384628</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.01600166410207748</v>
+        <v>0.002971913665533066</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.000658039003610611</v>
+        <v>0.1223925352096558</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.02353043481707573</v>
+        <v>0.08479971438646317</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.001387106254696846</v>
+        <v>0.1355126202106476</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.01797004789113998</v>
+        <v>0.03263052552938461</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.008191290311515331</v>
+        <v>0.01577172428369522</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.01483499724417925</v>
+        <v>0.06326793879270554</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.07562947273254395</v>
+        <v>0.2919529974460602</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.01815722696483135</v>
+        <v>0.03683583438396454</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.03098126128315926</v>
+        <v>0.07967416942119598</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0468234047293663</v>
+        <v>0.2118529677391052</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.02907797694206238</v>
+        <v>0.02643380686640739</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.01545749604701996</v>
+        <v>0.2059536725282669</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.02105859108269215</v>
+        <v>0.1214729771018028</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.0112916324287653</v>
+        <v>0.002979147247970104</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.007793604861944914</v>
+        <v>0.1027741953730583</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.05006313323974609</v>
+        <v>0.0375472865998745</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.01280665956437588</v>
+        <v>0.1215678527951241</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.06037153676152229</v>
+        <v>0.1457463502883911</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.09489315003156662</v>
+        <v>0.116488553583622</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.04412947222590446</v>
+        <v>0.06566685438156128</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.006275014020502567</v>
+        <v>0.10672477632761</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.006706149782985449</v>
+        <v>0.1583603769540787</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.009970603510737419</v>
+        <v>0.01387515012174845</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.008619766682386398</v>
+        <v>0.01016796566545963</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.009285056032240391</v>
+        <v>0.04987055063247681</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.00686959270387888</v>
+        <v>0.06478088349103928</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.02188623324036598</v>
+        <v>0.06107450649142265</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0001910814899019897</v>
+        <v>0.03631222620606422</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.008188752457499504</v>
+        <v>0.02047069184482098</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.02494356967508793</v>
+        <v>0.04449382424354553</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0104797538369894</v>
+        <v>0.1268854886293411</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.01177496369928122</v>
+        <v>0.04757024720311165</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0145825631916523</v>
+        <v>0.007794518023729324</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.05161365494132042</v>
+        <v>0.2264473438262939</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.002667550463229418</v>
+        <v>0.05794421955943108</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.0199083536863327</v>
+        <v>0.3261404633522034</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.03141935914754868</v>
+        <v>0.07489043474197388</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.00193663639947772</v>
+        <v>0.0293278694152832</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.004298810847103596</v>
+        <v>0.09335663914680481</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.005886521190404892</v>
+        <v>0.002924598520621657</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.02930511720478535</v>
+        <v>0.0163690522313118</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.005339994560927153</v>
+        <v>0.01262523140758276</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.02430110797286034</v>
+        <v>0.2158547639846802</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.00173273088876158</v>
+        <v>0.004946524277329445</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.02998505719006062</v>
+        <v>0.1246063485741615</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.005715752951800823</v>
+        <v>0.009266605600714684</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.008854684419929981</v>
+        <v>0.04546372219920158</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.008479282259941101</v>
+        <v>0.08459176123142242</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.00309392437338829</v>
+        <v>0.01839460246264935</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.0006691025337204337</v>
+        <v>0.02314426377415657</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.001358481356874108</v>
+        <v>0.06937055289745331</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.00110120652243495</v>
+        <v>0.2118014693260193</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.001800989964976907</v>
+        <v>0.2944740056991577</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0172771867364645</v>
+        <v>0.348571240901947</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.05740734562277794</v>
+        <v>0.1014057174324989</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.01330643240362406</v>
+        <v>0.2081231027841568</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.03453919664025307</v>
+        <v>0.193669319152832</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.02354790642857552</v>
+        <v>0.0206761509180069</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.00373479095287621</v>
+        <v>0.01582335494458675</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.005152496043592691</v>
+        <v>0.02832159027457237</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.02278447337448597</v>
+        <v>0.2055423855781555</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.004371141083538532</v>
+        <v>0.0142470421269536</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.02349788881838322</v>
+        <v>0.1464977264404297</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.009850725531578064</v>
+        <v>0.04140099510550499</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.02105208672583103</v>
+        <v>0.04456219077110291</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.01061337813735008</v>
+        <v>0.07298378646373749</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0003480447921901941</v>
+        <v>0.01158044952899218</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.006012547761201859</v>
+        <v>0.02102889865636826</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.002243557944893837</v>
+        <v>0.003198259975761175</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.06633327901363373</v>
+        <v>0.02276642620563507</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.02349170297384262</v>
+        <v>0.00429447740316391</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.04135753959417343</v>
+        <v>0.2159399539232254</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.01792309060692787</v>
+        <v>0.1325553208589554</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.02212728932499886</v>
+        <v>0.05830282717943192</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.000493926927447319</v>
+        <v>0.2123051583766937</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.0009443759918212891</v>
+        <v>0.2418053299188614</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.01537694595754147</v>
+        <v>0.08142803609371185</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.01372290402650833</v>
+        <v>0.0676288977265358</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.02059588022530079</v>
+        <v>0.0934816300868988</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.01547486428171396</v>
+        <v>0.05788495764136314</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.04895665496587753</v>
+        <v>0.1321233958005905</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.02494165115058422</v>
+        <v>0.03123786486685276</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0006682410603389144</v>
+        <v>0.02307640388607979</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.001724519766867161</v>
+        <v>0.0357927493751049</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.02000041306018829</v>
+        <v>0.1204668134450912</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.01315190270543098</v>
+        <v>0.2731033265590668</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.001803454128094018</v>
+        <v>0.04634831845760345</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0001271868823096156</v>
+        <v>0.01332116778939962</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.005095706321299076</v>
+        <v>0.06632713973522186</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.001140789361670613</v>
+        <v>0.03162408247590065</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.002320247702300549</v>
+        <v>0.1148616820573807</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.02881537564098835</v>
+        <v>0.1391193121671677</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.01290768850594759</v>
+        <v>0.1768417209386826</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.0008773221634328365</v>
+        <v>0.2069734334945679</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.0009276564233005047</v>
+        <v>0.1885766685009003</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.00016974494792521</v>
+        <v>0.1104830205440521</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.00325555307790637</v>
+        <v>0.1451115012168884</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.006168375723063946</v>
+        <v>0.1098127067089081</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.001673674676567316</v>
+        <v>0.02802773378789425</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.001680875197052956</v>
+        <v>0.1421502083539963</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.00856802798807621</v>
+        <v>0.1041461229324341</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.00214920099824667</v>
+        <v>0.02304631657898426</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.01216037571430206</v>
+        <v>0.04197228327393532</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.008760001510381699</v>
+        <v>0.0253825169056654</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.000426948769018054</v>
+        <v>0.09514924883842468</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.0143913496285677</v>
+        <v>0.2178006172180176</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.00330717209726572</v>
+        <v>0.04660802334547043</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.007071460597217083</v>
+        <v>0.1685722172260284</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.02307818457484245</v>
+        <v>0.08423913270235062</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.04120669513940811</v>
+        <v>0.04227482154965401</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.01229572109878063</v>
+        <v>0.03974705561995506</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.01404171995818615</v>
+        <v>0.1403608024120331</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.006866054609417915</v>
+        <v>0.001182838343083858</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.005664738826453686</v>
+        <v>0.006045653484761715</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.02482538670301437</v>
+        <v>0.2323021441698074</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.001240723417140543</v>
+        <v>0.0008310228586196899</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.02619905769824982</v>
+        <v>0.1876918226480484</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.007275337819010019</v>
+        <v>0.03410299867391586</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.0180349126458168</v>
+        <v>0.04193674772977829</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0157279297709465</v>
+        <v>0.07981722056865692</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.004761601332575083</v>
+        <v>0.04114043340086937</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.001106858951970935</v>
+        <v>9.310571476817131e-05</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0006766760488972068</v>
+        <v>0.01817475445568562</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.01845312863588333</v>
+        <v>0.1132885664701462</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.008335902355611324</v>
+        <v>0.04117574915289879</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.01151523739099503</v>
+        <v>0.1420865803956985</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.01324106007814407</v>
+        <v>0.02011140249669552</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.0231517031788826</v>
+        <v>0.09113481640815735</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.004624408669769764</v>
+        <v>0.04404644668102264</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.0214653592556715</v>
+        <v>0.04771894216537476</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.006955166347324848</v>
+        <v>0.05458612740039825</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.00914294645190239</v>
+        <v>0.09952642023563385</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.02935934066772461</v>
+        <v>0.3099561631679535</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.01016635727137327</v>
+        <v>0.02176094055175781</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.004924099892377853</v>
+        <v>0.09452858567237854</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.03293886035680771</v>
+        <v>0.256862610578537</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.008288704790174961</v>
+        <v>0.0100058987736702</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.05820749327540398</v>
+        <v>0.133448988199234</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.006465547252446413</v>
+        <v>0.2017935216426849</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.003792824223637581</v>
+        <v>0.1336269825696945</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0007599950768053532</v>
+        <v>0.02598955482244492</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.01385652273893356</v>
+        <v>0.06050232797861099</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.006802438758313656</v>
+        <v>0.0468432679772377</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.01373174879699945</v>
+        <v>0.1410131454467773</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.08395864814519882</v>
+        <v>0.05284326896071434</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.02481918036937714</v>
+        <v>0.03109857812523842</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.05725362524390221</v>
+        <v>0.04662109166383743</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.007945786230266094</v>
+        <v>0.08331212401390076</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.01181355956941843</v>
+        <v>0.02033818513154984</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.04966741055250168</v>
+        <v>0.006703290157020092</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1476506739854813</v>
+        <v>0.250282883644104</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04378611966967583</v>
+        <v>0.02372708916664124</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1417827606201172</v>
+        <v>0.239741787314415</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2576279640197754</v>
+        <v>0.01602103933691978</v>
       </c>
       <c r="F15" t="n">
-        <v>0.20000259578228</v>
+        <v>0.06303812563419342</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1112138032913208</v>
+        <v>0.04207809269428253</v>
       </c>
       <c r="H15" t="n">
-        <v>0.05671815574169159</v>
+        <v>0.01376385986804962</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1217257231473923</v>
+        <v>0.06004438549280167</v>
       </c>
       <c r="J15" t="n">
-        <v>0.08148683607578278</v>
+        <v>0.02299920469522476</v>
       </c>
       <c r="K15" t="n">
-        <v>0.06563463062047958</v>
+        <v>0.3206673860549927</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01298161596059799</v>
+        <v>0.06781837344169617</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1377876698970795</v>
+        <v>0.2750751972198486</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2181730568408966</v>
+        <v>0.02298469096422195</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1034800261259079</v>
+        <v>0.1226272210478783</v>
       </c>
       <c r="P15" t="n">
-        <v>0.04561899602413177</v>
+        <v>0.006291169673204422</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.07793068885803223</v>
+        <v>0.0758533775806427</v>
       </c>
       <c r="R15" t="n">
-        <v>0.09435752034187317</v>
+        <v>0.03860189020633698</v>
       </c>
       <c r="S15" t="n">
-        <v>0.01451932638883591</v>
+        <v>0.00502133509144187</v>
       </c>
       <c r="T15" t="n">
-        <v>0.007003224454820156</v>
+        <v>0.04073608666658401</v>
       </c>
       <c r="U15" t="n">
-        <v>0.05124014988541603</v>
+        <v>0.01058841124176979</v>
       </c>
       <c r="V15" t="n">
-        <v>0.108162447810173</v>
+        <v>0.02779215946793556</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1736438721418381</v>
+        <v>0.02499398961663246</v>
       </c>
       <c r="X15" t="n">
-        <v>0.003004615660756826</v>
+        <v>0.02386914938688278</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.01995348185300827</v>
+        <v>0.00871460884809494</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.03702054917812347</v>
+        <v>0.02591272629797459</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.04983071982860565</v>
+        <v>0.06112539023160934</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.03679622709751129</v>
+        <v>0.04241156578063965</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.07872673869132996</v>
+        <v>0.04637550190091133</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.1231985315680504</v>
+        <v>0.02069734595716</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.03657511621713638</v>
+        <v>0.02802919782698154</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.056638203561306</v>
+        <v>0.1522244811058044</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.02058441936969757</v>
+        <v>0.06486533582210541</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.02944206073880196</v>
+        <v>0.01489920169115067</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.06831051409244537</v>
+        <v>0.02021141536533833</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.1000531911849976</v>
+        <v>0.01753394305706024</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.0240405835211277</v>
+        <v>0.01291673816740513</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.03120988421142101</v>
+        <v>0.03756794333457947</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.009889727458357811</v>
+        <v>0.01271749474108219</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.07261491566896439</v>
+        <v>0.03570732101798058</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.005904311314225197</v>
+        <v>0.07264874130487442</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.01070646662265062</v>
+        <v>0.02015481144189835</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.04515756294131279</v>
+        <v>0.02859731204807758</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.0386628657579422</v>
+        <v>0.04198071360588074</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.03778652101755142</v>
+        <v>0.02854113280773163</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.06044142320752144</v>
+        <v>0.03943199291825294</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.02285652421414852</v>
+        <v>0.03972802683711052</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.09258657693862915</v>
+        <v>0.01753523014485836</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.03774760290980339</v>
+        <v>0.1371437013149261</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.213341623544693</v>
+        <v>0.09158162772655487</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.1737181842327118</v>
+        <v>0.04780935123562813</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.1952494829893112</v>
+        <v>0.003476782701909542</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.03715326637029648</v>
+        <v>0.1146260052919388</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.1061955690383911</v>
+        <v>0.09074660390615463</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.02317168563604355</v>
+        <v>0.03890733048319817</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.08089941740036011</v>
+        <v>0.09413157403469086</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.01199213042855263</v>
+        <v>0.05178285390138626</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.2685357332229614</v>
+        <v>0.02368311583995819</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.2810813784599304</v>
+        <v>0.005901293829083443</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.03927721083164215</v>
+        <v>0.01422507036477327</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.1757026463747025</v>
+        <v>0.009424367919564247</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.008017978630959988</v>
+        <v>0.1206374391913414</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.06057221069931984</v>
+        <v>0.03443878889083862</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.008776217699050903</v>
+        <v>0.01180148869752884</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.02517291344702244</v>
+        <v>0.08452747762203217</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.02299828641116619</v>
+        <v>0.01802997477352619</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.06165381893515587</v>
+        <v>0.04742527008056641</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0859382376074791</v>
+        <v>0.01686182618141174</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.05204086750745773</v>
+        <v>0.02083838544785976</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.1716395914554596</v>
+        <v>0.01477360259741545</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.001751587609760463</v>
+        <v>0.05759645625948906</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.0290475245565176</v>
+        <v>0.00632846262305975</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.001710034906864166</v>
+        <v>0.009223021566867828</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.001788066467270255</v>
+        <v>0.02647662535309792</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.0005586035549640656</v>
+        <v>0.01196683011949062</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.02193097397685051</v>
+        <v>0.0891951397061348</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.1913887858390808</v>
+        <v>0.01447959803044796</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.02871143072843552</v>
+        <v>0.0481732115149498</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.120043009519577</v>
+        <v>0.005320747382938862</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.05611307919025421</v>
+        <v>0.04532746225595474</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.1075241789221764</v>
+        <v>0.04355127364397049</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.02016713470220566</v>
+        <v>0.003781765233725309</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.01160313189029694</v>
+        <v>0.08664419502019882</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.02105719968676567</v>
+        <v>0.006195084191858768</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.05949924513697624</v>
+        <v>0.06797130405902863</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.02454156242311001</v>
+        <v>0.006134139373898506</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.03222160786390305</v>
+        <v>0.02965725027024746</v>
       </c>
       <c r="CJ15" t="n">
-        <v>6.453879177570343e-05</v>
+        <v>0.007914597168564796</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.02239870652556419</v>
+        <v>0.008419713005423546</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.01124594639986753</v>
+        <v>0.00718039134517312</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.05378780514001846</v>
+        <v>0.01690469309687614</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.09085658192634583</v>
+        <v>0.01089799404144287</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.03693127632141113</v>
+        <v>0.06331001967191696</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.227637842297554</v>
+        <v>0.05026964098215103</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.2959787249565125</v>
+        <v>0.1891143918037415</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.08356401324272156</v>
+        <v>0.04812095686793327</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.0899084210395813</v>
+        <v>0.01547391805797815</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.09619009494781494</v>
+        <v>0.07943273335695267</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.01664398238062859</v>
+        <v>0.02251508273184299</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.01106912456452847</v>
+        <v>0.0007859077304601669</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.02055462077260017</v>
+        <v>0.07886740565299988</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.01389832515269518</v>
+        <v>0.001020069932565093</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.02702505141496658</v>
+        <v>0.07636456191539764</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.02802114747464657</v>
+        <v>0.006669927388429642</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.03799693286418915</v>
+        <v>0.02860773168504238</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.009818460792303085</v>
+        <v>0.004689156077802181</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.004982314072549343</v>
+        <v>0.007373998872935772</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.03787136822938919</v>
+        <v>0.01936992630362511</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.01357612758874893</v>
+        <v>0.02940277010202408</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.1183664798736572</v>
+        <v>0.08577244728803635</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.0188112985342741</v>
+        <v>0.0119280107319355</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.05386701971292496</v>
+        <v>0.06249088793992996</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.1013593971729279</v>
+        <v>0.06010181829333305</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.09516658633947372</v>
+        <v>0.009305233135819435</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.03664079308509827</v>
+        <v>0.04298438876867294</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.1083894148468971</v>
+        <v>0.08722265064716339</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.0449841246008873</v>
+        <v>0.02485622093081474</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.01962243393063545</v>
+        <v>0.002603780478239059</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.07625159621238708</v>
+        <v>0.02630840055644512</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.01645456627011299</v>
+        <v>0.02661014534533024</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.212555930018425</v>
+        <v>0.07242581248283386</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.1806102395057678</v>
+        <v>0.04810813069343567</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.1771031320095062</v>
+        <v>0.002365035237744451</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.03730294853448868</v>
+        <v>0.02452327683568001</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.06059073656797409</v>
+        <v>0.06820723414421082</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.02613987028598785</v>
+        <v>0.06596505641937256</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.02174537070095539</v>
+        <v>0.0008646459318697453</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.02686660178005695</v>
+        <v>0.05591155961155891</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.04716358706355095</v>
+        <v>0.007402132265269756</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.001370164100080729</v>
+        <v>0.0618990994989872</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.0639498382806778</v>
+        <v>0.04266268387436867</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.02284926548600197</v>
+        <v>0.04297353327274323</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.127365842461586</v>
+        <v>0.05838129669427872</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.1700231730937958</v>
+        <v>0.1182417199015617</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.1100135520100594</v>
+        <v>0.04398581013083458</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.04659232497215271</v>
+        <v>0.001781263621523976</v>
       </c>
       <c r="EG15" t="n">
-        <v>8.991919457912445e-05</v>
+        <v>0.1206144765019417</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.04237784445285797</v>
+        <v>0.003216985147446394</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.1361923664808273</v>
+        <v>0.03626716509461403</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.1197758093476295</v>
+        <v>0.02209699153900146</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.05224248766899109</v>
+        <v>0.02385727688670158</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.006557490676641464</v>
+        <v>0.0111029390245676</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.09605506062507629</v>
+        <v>0.01189320720732212</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.01904300041496754</v>
+        <v>0.008425639942288399</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.03859259933233261</v>
+        <v>0.01225835643708706</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.06725014746189117</v>
+        <v>0.04911767691373825</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.009928964078426361</v>
+        <v>0.02925428189337254</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.006869291886687279</v>
+        <v>0.08796307444572449</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.05993694812059402</v>
+        <v>0.05173796787858009</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.1757265478372574</v>
+        <v>0.007206247188150883</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.0008070701733231544</v>
+        <v>0.02854466810822487</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.006659485399723053</v>
+        <v>0.06341303884983063</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.03811201825737953</v>
+        <v>0.02071735449135303</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.02541914209723473</v>
+        <v>0.004367727786302567</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.01370387431234121</v>
+        <v>0.07770944386720657</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.005274359136819839</v>
+        <v>0.01424049958586693</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.04265093058347702</v>
+        <v>0.08357188850641251</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.04608007520437241</v>
+        <v>0.003745649009943008</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.04131782799959183</v>
+        <v>0.0297793373465538</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.02677316218614578</v>
+        <v>0.003056999295949936</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.002673357725143433</v>
+        <v>0.01683118380606174</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.01346011180430651</v>
+        <v>0.009110363200306892</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.0298811998218298</v>
+        <v>0.005984022282063961</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.1376726627349854</v>
+        <v>0.03778783231973648</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.09248591214418411</v>
+        <v>0.01590358279645443</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.02847671508789062</v>
+        <v>0.05967462062835693</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.09522442519664764</v>
+        <v>0.06904688477516174</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.07303882390260696</v>
+        <v>0.02134937793016434</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.09608428925275803</v>
+        <v>0.008050089702010155</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.04025577008724213</v>
+        <v>0.06808242946863174</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.06919564306735992</v>
+        <v>0.07104562222957611</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.08539390563964844</v>
+        <v>0.000909510999917984</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.08150556683540344</v>
+        <v>0.02322686463594437</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.06141851842403412</v>
+        <v>0.0643007755279541</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.1280750036239624</v>
+        <v>0.09590878337621689</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.2918100655078888</v>
+        <v>0.1294811069965363</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.07280909270048141</v>
+        <v>0.1024322509765625</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.2070415914058685</v>
+        <v>0.02242710068821907</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.01729526370763779</v>
+        <v>0.02081541158258915</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.007848531939089298</v>
+        <v>0.01179584860801697</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.02026910707354546</v>
+        <v>0.005890245549380779</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.05148264765739441</v>
+        <v>0.04441861063241959</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.01654068008065224</v>
+        <v>0.02851114794611931</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.001112494617700577</v>
+        <v>0.0001142248511314392</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.1337976455688477</v>
+        <v>0.1088003367185593</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.02161900699138641</v>
+        <v>0.01442501693964005</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.1691654026508331</v>
+        <v>0.04678656160831451</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.02602415531873703</v>
+        <v>0.05890663713216782</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.03305090963840485</v>
+        <v>0.022994264960289</v>
       </c>
     </row>
   </sheetData>
